--- a/input_data/example_model.xlsx
+++ b/input_data/example_model.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="27328"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dsdennis\HOPE\Predicer\input_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{7CCF147E-52C5-4D97-981B-C870745EFBBD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01DF83F7-EE22-422F-A6C0-4C829A97F6A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="17640" tabRatio="796" activeTab="1" xr2:uid="{788BFBD1-D930-4535-8A91-D85C56924796}"/>
+    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="796" firstSheet="4" activeTab="14" xr2:uid="{788BFBD1-D930-4535-8A91-D85C56924796}"/>
   </bookViews>
   <sheets>
     <sheet name="timeseries" sheetId="18" r:id="rId1"/>
@@ -27,20 +27,21 @@
     <sheet name="cf" sheetId="7" r:id="rId12"/>
     <sheet name="inflow" sheetId="3" r:id="rId13"/>
     <sheet name="inflow_blocks" sheetId="22" r:id="rId14"/>
-    <sheet name="price" sheetId="4" r:id="rId15"/>
-    <sheet name="markets" sheetId="5" r:id="rId16"/>
-    <sheet name="bid_slots" sheetId="28" r:id="rId17"/>
-    <sheet name="reserve_realisation" sheetId="23" r:id="rId18"/>
-    <sheet name="market_prices" sheetId="8" r:id="rId19"/>
-    <sheet name="balance_prices" sheetId="20" r:id="rId20"/>
-    <sheet name="reserve_activation_price" sheetId="27" r:id="rId21"/>
-    <sheet name="risk" sheetId="17" r:id="rId22"/>
-    <sheet name="scenarios" sheetId="9" r:id="rId23"/>
-    <sheet name="fixed_ts" sheetId="11" r:id="rId24"/>
-    <sheet name="eff_ts" sheetId="12" r:id="rId25"/>
-    <sheet name="cap_ts" sheetId="16" r:id="rId26"/>
-    <sheet name="constraints" sheetId="14" r:id="rId27"/>
-    <sheet name="gen_constraint" sheetId="15" r:id="rId28"/>
+    <sheet name="flex_inflow" sheetId="29" r:id="rId15"/>
+    <sheet name="price" sheetId="4" r:id="rId16"/>
+    <sheet name="markets" sheetId="5" r:id="rId17"/>
+    <sheet name="bid_slots" sheetId="28" r:id="rId18"/>
+    <sheet name="reserve_realisation" sheetId="23" r:id="rId19"/>
+    <sheet name="market_prices" sheetId="8" r:id="rId20"/>
+    <sheet name="balance_prices" sheetId="20" r:id="rId21"/>
+    <sheet name="reserve_activation_price" sheetId="27" r:id="rId22"/>
+    <sheet name="risk" sheetId="17" r:id="rId23"/>
+    <sheet name="scenarios" sheetId="9" r:id="rId24"/>
+    <sheet name="fixed_ts" sheetId="11" r:id="rId25"/>
+    <sheet name="eff_ts" sheetId="12" r:id="rId26"/>
+    <sheet name="cap_ts" sheetId="16" r:id="rId27"/>
+    <sheet name="constraints" sheetId="14" r:id="rId28"/>
+    <sheet name="gen_constraint" sheetId="15" r:id="rId29"/>
   </sheets>
   <calcPr calcId="191029"/>
   <extLst>
@@ -60,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="190" uniqueCount="128">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="133">
   <si>
     <t>node</t>
   </si>
@@ -444,6 +445,21 @@
   </si>
   <si>
     <t>common_end_timesteps</t>
+  </si>
+  <si>
+    <t>period_name</t>
+  </si>
+  <si>
+    <t>scenario</t>
+  </si>
+  <si>
+    <t>t_start</t>
+  </si>
+  <si>
+    <t>t_end</t>
+  </si>
+  <si>
+    <t>inflow</t>
   </si>
 </sst>
 </file>
@@ -496,13 +512,10 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="9">
+  <cellXfs count="6">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="2" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyNumberFormat="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -3815,9 +3828,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office 2013 - 2022 Theme">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2013 - 2022">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -3855,7 +3868,7 @@
         <a:srgbClr val="954F72"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2013 - 2022">
       <a:majorFont>
         <a:latin typeface="Calibri Light" panose="020F0302020204030204"/>
         <a:ea typeface=""/>
@@ -3961,7 +3974,7 @@
         <a:font script="Tfng" typeface="Ebrima"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2013 - 2022">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -4103,7 +4116,7 @@
   <a:extraClrSchemeLst/>
   <a:extLst>
     <a:ext uri="{05A4C25C-085E-4340-85A3-A5531E510DB2}">
-      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
+      <thm15:themeFamily xmlns:thm15="http://schemas.microsoft.com/office/thememl/2012/main" name="Office 2013 - 2022 Theme" id="{62F939B6-93AF-4DB8-9C6B-D6C7DFDC589F}" vid="{4A3C46E8-61CC-4603-A589-7422A47A8E4A}"/>
     </a:ext>
   </a:extLst>
 </a:theme>
@@ -4112,179 +4125,179 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39053E69-3A75-490E-847C-66A9CF6C1FC5}">
   <dimension ref="A1:A49"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
         <v>44671</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
         <v>44671.041666666664</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
         <v>44671.08333321759</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
         <v>44671.124999826388</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
         <v>44671.166666435187</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
         <v>44671.208333043978</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
         <v>44671.249999537038</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
         <v>44671.291666087964</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
         <v>44671.333332638889</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
         <v>44671.374999189815</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="8"/>
-    </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="8"/>
-    </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="8"/>
-    </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="8"/>
-    </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="8"/>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="8"/>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="8"/>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="8"/>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="8"/>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="8"/>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="8"/>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="8"/>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="8"/>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="8"/>
-    </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A26" s="8"/>
-    </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A27" s="8"/>
-    </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A28" s="8"/>
-    </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A29" s="8"/>
-    </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A30" s="8"/>
-    </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A31" s="8"/>
-    </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A32" s="8"/>
-    </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A33" s="8"/>
-    </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A34" s="8"/>
-    </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A35" s="8"/>
-    </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A36" s="8"/>
-    </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A37" s="8"/>
-    </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A38" s="8"/>
-    </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A39" s="8"/>
-    </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A40" s="8"/>
-    </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A41" s="8"/>
-    </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A42" s="8"/>
-    </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A43" s="8"/>
-    </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A44" s="8"/>
-    </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A45" s="8"/>
-    </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A46" s="8"/>
-    </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A47" s="8"/>
-    </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A48" s="8"/>
-    </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A49" s="8"/>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" s="5"/>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" s="5"/>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" s="5"/>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" s="5"/>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" s="5"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="5"/>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="5"/>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="5"/>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="5"/>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="5"/>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="5"/>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="5"/>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="5"/>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="5"/>
+    </row>
+    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A26" s="5"/>
+    </row>
+    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A27" s="5"/>
+    </row>
+    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A28" s="5"/>
+    </row>
+    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A29" s="5"/>
+    </row>
+    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A30" s="5"/>
+    </row>
+    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A31" s="5"/>
+    </row>
+    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A32" s="5"/>
+    </row>
+    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A33" s="5"/>
+    </row>
+    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A34" s="5"/>
+    </row>
+    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A35" s="5"/>
+    </row>
+    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A36" s="5"/>
+    </row>
+    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A37" s="5"/>
+    </row>
+    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A38" s="5"/>
+    </row>
+    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A39" s="5"/>
+    </row>
+    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A40" s="5"/>
+    </row>
+    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A41" s="5"/>
+    </row>
+    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A42" s="5"/>
+    </row>
+    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A43" s="5"/>
+    </row>
+    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A44" s="5"/>
+    </row>
+    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A45" s="5"/>
+    </row>
+    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A46" s="5"/>
+    </row>
+    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A47" s="5"/>
+    </row>
+    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A48" s="5"/>
+    </row>
+    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A49" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4295,74 +4308,74 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8F1FEF7-A337-4ADD-8F2A-03D982D23844}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="8" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="3"/>
-      <c r="C1" s="3"/>
-    </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
+      <c r="B1" s="2"/>
+      <c r="C1" s="2"/>
+    </row>
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.124999826388</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666435187</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44671.208333043978</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44671.249999537038</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44671.291666087964</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44671.333332638889</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>44671.374999189815</v>
       </c>
@@ -4376,17 +4389,17 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0532F8A-0FB4-47AD-98A1-4065D3376432}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>41</v>
       </c>
@@ -4402,27 +4415,27 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77A4637A-7829-48D6-AE54-2E654AB1A427}">
   <dimension ref="A1:L25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="8" customWidth="1"/>
-    <col min="2" max="5" width="12.5703125" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="5.5703125" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="5" customWidth="1"/>
+    <col min="2" max="5" width="12.5546875" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>74</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
       </c>
@@ -4432,11 +4445,11 @@
       <c r="C2">
         <v>0.54</v>
       </c>
-      <c r="F2" s="8"/>
-      <c r="L2" s="8"/>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
+      <c r="F2" s="5"/>
+      <c r="L2" s="5"/>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
       </c>
@@ -4447,8 +4460,8 @@
         <v>0.52</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
       </c>
@@ -4459,8 +4472,8 @@
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.124999826388</v>
       </c>
@@ -4471,8 +4484,8 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666435187</v>
       </c>
@@ -4483,8 +4496,8 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44671.208333043978</v>
       </c>
@@ -4495,8 +4508,8 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44671.249999537038</v>
       </c>
@@ -4507,8 +4520,8 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44671.291666087964</v>
       </c>
@@ -4519,8 +4532,8 @@
         <v>0.47</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44671.333332638889</v>
       </c>
@@ -4531,8 +4544,8 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>44671.374999189815</v>
       </c>
@@ -4543,86 +4556,86 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="str">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="str">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="str">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="str">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="str">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="str">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="str">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="str">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="8" t="str">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="str">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="8" t="str">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="5" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="str">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="5" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="str">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="5" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="str">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="5" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
       </c>
@@ -4638,26 +4651,26 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F87DD44-A1AD-4241-AED7-C48CC9DEE2E2}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="8" customWidth="1"/>
-    <col min="4" max="6" width="10.42578125" customWidth="1"/>
-    <col min="7" max="7" width="10.42578125" style="1" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="5" customWidth="1"/>
+    <col min="4" max="6" width="10.44140625" customWidth="1"/>
+    <col min="7" max="7" width="10.44140625" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>76</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
       </c>
@@ -4667,11 +4680,10 @@
       <c r="C2">
         <v>-4</v>
       </c>
-      <c r="F2" s="2"/>
-      <c r="G2" s="2"/>
-    </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
+      <c r="G2"/>
+    </row>
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
       </c>
@@ -4681,11 +4693,10 @@
       <c r="C3">
         <v>-9</v>
       </c>
-      <c r="F3" s="2"/>
-      <c r="G3" s="2"/>
-    </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
+      <c r="G3"/>
+    </row>
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
       </c>
@@ -4695,11 +4706,10 @@
       <c r="C4">
         <v>-4</v>
       </c>
-      <c r="F4" s="2"/>
-      <c r="G4" s="2"/>
-    </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
+      <c r="G4"/>
+    </row>
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.124999826388</v>
       </c>
@@ -4709,11 +4719,10 @@
       <c r="C5">
         <v>-6</v>
       </c>
-      <c r="F5" s="2"/>
-      <c r="G5" s="2"/>
-    </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
+      <c r="G5"/>
+    </row>
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666435187</v>
       </c>
@@ -4723,11 +4732,10 @@
       <c r="C6">
         <v>-6</v>
       </c>
-      <c r="F6" s="2"/>
-      <c r="G6" s="2"/>
-    </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
+      <c r="G6"/>
+    </row>
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44671.208333043978</v>
       </c>
@@ -4737,11 +4745,10 @@
       <c r="C7">
         <v>-6</v>
       </c>
-      <c r="F7" s="2"/>
-      <c r="G7" s="2"/>
-    </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
+      <c r="G7"/>
+    </row>
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44671.249999537038</v>
       </c>
@@ -4751,11 +4758,10 @@
       <c r="C8">
         <v>-8</v>
       </c>
-      <c r="F8" s="2"/>
-      <c r="G8" s="2"/>
-    </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
+      <c r="G8"/>
+    </row>
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44671.291666087964</v>
       </c>
@@ -4765,11 +4771,10 @@
       <c r="C9">
         <v>-9</v>
       </c>
-      <c r="F9" s="2"/>
-      <c r="G9" s="2"/>
-    </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
+      <c r="G9"/>
+    </row>
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44671.333332638889</v>
       </c>
@@ -4779,11 +4784,10 @@
       <c r="C10">
         <v>-3</v>
       </c>
-      <c r="F10" s="2"/>
-      <c r="G10" s="2"/>
-    </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
+      <c r="G10"/>
+    </row>
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>44671.374999189815</v>
       </c>
@@ -4793,120 +4797,105 @@
       <c r="C11">
         <v>-9</v>
       </c>
-      <c r="F11" s="2"/>
-      <c r="G11" s="2"/>
-    </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="str">
+      <c r="G11"/>
+    </row>
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
-      <c r="F12" s="2"/>
-      <c r="G12" s="2"/>
-    </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="str">
+      <c r="G12"/>
+    </row>
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
-      <c r="F13" s="2"/>
-      <c r="G13" s="2"/>
-    </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="str">
+      <c r="G13"/>
+    </row>
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
-      <c r="F14" s="2"/>
-      <c r="G14" s="2"/>
-    </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="str">
+      <c r="G14"/>
+    </row>
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
-      <c r="F15" s="2"/>
-      <c r="G15" s="2"/>
-    </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="str">
+      <c r="G15"/>
+    </row>
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
-      <c r="F16" s="2"/>
-      <c r="G16" s="2"/>
-    </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="str">
+      <c r="G16"/>
+    </row>
+    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
-      <c r="F17" s="2"/>
-      <c r="G17" s="2"/>
-    </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="str">
+      <c r="G17"/>
+    </row>
+    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
-      <c r="F18" s="2"/>
-      <c r="G18" s="2"/>
-    </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="str">
+      <c r="G18"/>
+    </row>
+    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
-      <c r="F19" s="2"/>
-      <c r="G19" s="2"/>
-    </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A20" s="8" t="str">
+      <c r="G19"/>
+    </row>
+    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
-      <c r="F20" s="2"/>
-      <c r="G20" s="2"/>
-    </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="str">
+      <c r="G20"/>
+    </row>
+    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
-      <c r="F21" s="2"/>
-      <c r="G21" s="2"/>
-    </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A22" s="8" t="str">
+      <c r="G21"/>
+    </row>
+    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A22" s="5" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
-      <c r="F22" s="2"/>
-      <c r="G22" s="2"/>
-    </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="str">
+      <c r="G22"/>
+    </row>
+    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A23" s="5" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
-      <c r="F23" s="2"/>
-      <c r="G23" s="2"/>
-    </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="str">
+      <c r="G23"/>
+    </row>
+    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A24" s="5" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
-      <c r="F24" s="2"/>
-      <c r="G24" s="2"/>
-    </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="str">
+      <c r="G24"/>
+    </row>
+    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A25" s="5" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
       </c>
-      <c r="F25" s="2"/>
-      <c r="G25" s="2"/>
+      <c r="G25"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -4918,86 +4907,86 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E44A96C9-CA4B-4735-AF1E-65BD86DB3657}">
   <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="3" max="6" width="13.28515625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.7109375" customWidth="1"/>
+    <col min="3" max="6" width="13.33203125" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.6640625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A2">
         <v>1</v>
       </c>
-      <c r="C2" s="8"/>
-      <c r="E2" s="8"/>
-    </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C2" s="5"/>
+      <c r="E2" s="5"/>
+    </row>
+    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A3">
         <v>2</v>
       </c>
-      <c r="C3" s="8"/>
-      <c r="E3" s="8"/>
-    </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C3" s="5"/>
+      <c r="E3" s="5"/>
+    </row>
+    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A4">
         <v>3</v>
       </c>
-      <c r="C4" s="8"/>
-      <c r="E4" s="8"/>
-    </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C4" s="5"/>
+      <c r="E4" s="5"/>
+    </row>
+    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A5">
         <v>4</v>
       </c>
-      <c r="C5" s="8"/>
-      <c r="E5" s="8"/>
-    </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
+      <c r="C5" s="5"/>
+      <c r="E5" s="5"/>
+    </row>
+    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A6">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A7">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A8">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A9">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A10">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
       <c r="A11">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
-      <c r="C15" s="8"/>
-      <c r="D15" s="8"/>
-      <c r="E15" s="8"/>
-      <c r="F15" s="8"/>
-    </row>
-    <row r="17" spans="3:6" x14ac:dyDescent="0.25">
-      <c r="C17" s="8"/>
-      <c r="D17" s="8"/>
-      <c r="E17" s="8"/>
-      <c r="F17" s="8"/>
+    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="C15" s="5"/>
+      <c r="D15" s="5"/>
+      <c r="E15" s="5"/>
+      <c r="F15" s="5"/>
+    </row>
+    <row r="17" spans="3:6" x14ac:dyDescent="0.3">
+      <c r="C17" s="5"/>
+      <c r="D17" s="5"/>
+      <c r="E17" s="5"/>
+      <c r="F17" s="5"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -5005,26 +4994,60 @@
 </file>
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBF5682F-29D1-41D2-B323-E6C39BD83827}">
+  <dimension ref="A1:F1"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+      <c r="A1" t="s">
+        <v>128</v>
+      </c>
+      <c r="B1" t="s">
+        <v>0</v>
+      </c>
+      <c r="C1" t="s">
+        <v>129</v>
+      </c>
+      <c r="D1" t="s">
+        <v>130</v>
+      </c>
+      <c r="E1" t="s">
+        <v>131</v>
+      </c>
+      <c r="F1" t="s">
+        <v>132</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02307C1F-427B-487D-B703-EBF512D7AC27}">
   <dimension ref="A1:C25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="8" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>62</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
       </c>
@@ -5035,8 +5058,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
       </c>
@@ -5047,8 +5070,8 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
       </c>
@@ -5059,8 +5082,8 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.124999826388</v>
       </c>
@@ -5071,8 +5094,8 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666435187</v>
       </c>
@@ -5083,8 +5106,8 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44671.208333043978</v>
       </c>
@@ -5095,8 +5118,8 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44671.249999537038</v>
       </c>
@@ -5107,8 +5130,8 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44671.291666087964</v>
       </c>
@@ -5119,8 +5142,8 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44671.333332638889</v>
       </c>
@@ -5131,8 +5154,8 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>44671.374999189815</v>
       </c>
@@ -5143,86 +5166,86 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="str">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="str">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="str">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="str">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="str">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="str">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="str">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="str">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="8" t="str">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="str">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="8" t="str">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="5" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="str">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="5" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="str">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="5" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="str">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="5" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
       </c>
@@ -5233,174 +5256,174 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3788A93-7501-4F5D-9E8F-38D329CC85EC}">
   <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="11" style="7" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.7109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.5703125" style="7" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.85546875" style="7" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.28515625" style="7" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.42578125" style="7" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.7109375" style="7" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.140625" style="7"/>
+    <col min="1" max="1" width="11" style="4" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="7.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.5546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.88671875" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.33203125" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.44140625" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.6640625" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.109375" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>25</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>124</v>
       </c>
-      <c r="C1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="3" t="s">
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>96</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>30</v>
       </c>
-      <c r="F1" s="6" t="s">
+      <c r="F1" s="3" t="s">
         <v>37</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>42</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>51</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>90</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>91</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>92</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>93</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A2" s="7" t="s">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" s="4" t="s">
         <v>10</v>
       </c>
-      <c r="B2" s="7" t="s">
+      <c r="B2" s="4" t="s">
         <v>29</v>
       </c>
-      <c r="C2" s="7" t="s">
+      <c r="C2" s="4" t="s">
         <v>8</v>
       </c>
-      <c r="D2" s="7" t="s">
+      <c r="D2" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="E2" s="7" t="s">
+      <c r="E2" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="F2" s="7">
-        <v>0</v>
-      </c>
-      <c r="G2" s="7" t="s">
+      <c r="F2" s="4">
+        <v>0</v>
+      </c>
+      <c r="G2" s="4" t="s">
         <v>31</v>
       </c>
-      <c r="H2" s="7">
+      <c r="H2" s="4">
         <v>1</v>
       </c>
       <c r="I2">
         <v>0</v>
       </c>
-      <c r="J2" s="7">
-        <v>0</v>
-      </c>
-      <c r="K2" s="7">
-        <v>0</v>
-      </c>
-      <c r="L2" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A3" s="7" t="s">
+      <c r="J2" s="4">
+        <v>0</v>
+      </c>
+      <c r="K2" s="4">
+        <v>0</v>
+      </c>
+      <c r="L2" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" s="4" t="s">
         <v>59</v>
       </c>
-      <c r="B3" s="7" t="s">
+      <c r="B3" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C3" s="7" t="s">
+      <c r="C3" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="D3" s="7" t="s">
+      <c r="D3" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="E3" s="7" t="s">
+      <c r="E3" s="4" t="s">
         <v>43</v>
       </c>
-      <c r="F3" s="7">
+      <c r="F3" s="4">
         <v>0.2</v>
       </c>
-      <c r="G3" s="7" t="s">
+      <c r="G3" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="H3" s="7">
+      <c r="H3" s="4">
         <v>1</v>
       </c>
       <c r="I3">
         <v>1</v>
       </c>
-      <c r="J3" s="7">
-        <v>0</v>
-      </c>
-      <c r="K3" s="7">
-        <v>0</v>
-      </c>
-      <c r="L3" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
-      <c r="A4" s="7" t="s">
+      <c r="J3" s="4">
+        <v>0</v>
+      </c>
+      <c r="K3" s="4">
+        <v>0</v>
+      </c>
+      <c r="L3" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A4" s="4" t="s">
         <v>78</v>
       </c>
-      <c r="B4" s="7" t="s">
+      <c r="B4" s="4" t="s">
         <v>28</v>
       </c>
-      <c r="C4" s="7" t="s">
+      <c r="C4" s="4" t="s">
         <v>97</v>
       </c>
-      <c r="D4" s="7" t="s">
+      <c r="D4" s="4" t="s">
         <v>98</v>
       </c>
-      <c r="E4" s="7" t="s">
+      <c r="E4" s="4" t="s">
         <v>79</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="4">
         <v>0.2</v>
       </c>
-      <c r="G4" s="7" t="s">
+      <c r="G4" s="4" t="s">
         <v>41</v>
       </c>
-      <c r="H4" s="7">
+      <c r="H4" s="4">
         <v>1</v>
       </c>
       <c r="I4">
         <v>1</v>
       </c>
-      <c r="J4" s="7">
-        <v>0</v>
-      </c>
-      <c r="K4" s="7">
-        <v>0</v>
-      </c>
-      <c r="L4" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
+      <c r="J4" s="4">
+        <v>0</v>
+      </c>
+      <c r="K4" s="4">
+        <v>0</v>
+      </c>
+      <c r="L4" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
       <c r="I5"/>
     </row>
   </sheetData>
@@ -5408,75 +5431,75 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7B04689-3483-4889-8469-CD5E284D12AD}">
   <dimension ref="A1:A11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="8" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.124999826388</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666435187</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44671.208333043978</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44671.249999537038</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44671.291666087964</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44671.333332638889</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>44671.374999189815</v>
       </c>
@@ -5487,34 +5510,34 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3E266E0-7523-413E-8B0C-F3E2413808A5}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="8" customWidth="1"/>
-    <col min="2" max="3" width="6.5703125" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="5" customWidth="1"/>
+    <col min="2" max="3" width="6.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="4" t="s">
         <v>121</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
       </c>
@@ -5531,8 +5554,8 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
       </c>
@@ -5549,8 +5572,8 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
       </c>
@@ -5567,8 +5590,8 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.124999826388</v>
       </c>
@@ -5585,8 +5608,8 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666435187</v>
       </c>
@@ -5603,8 +5626,8 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44671.208333043978</v>
       </c>
@@ -5621,8 +5644,8 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44671.249999537038</v>
       </c>
@@ -5639,8 +5662,8 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44671.291666087964</v>
       </c>
@@ -5657,8 +5680,8 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44671.333332638889</v>
       </c>
@@ -5675,8 +5698,8 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>44671.374999189815</v>
       </c>
@@ -5699,41 +5722,141 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5112C03D-AA3C-4BDB-99A8-E263BCF7A011}">
+  <dimension ref="A1:B11"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="27" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.88671875" bestFit="1" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>110</v>
+      </c>
+      <c r="B2">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>111</v>
+      </c>
+      <c r="B3">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
+        <v>112</v>
+      </c>
+      <c r="B4">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
+        <v>113</v>
+      </c>
+      <c r="B5">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A6" t="s">
+        <v>114</v>
+      </c>
+      <c r="B6">
+        <v>1</v>
+      </c>
+    </row>
+    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A7" t="s">
+        <v>116</v>
+      </c>
+      <c r="B7">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A8" t="s">
+        <v>117</v>
+      </c>
+      <c r="B8">
+        <v>10000</v>
+      </c>
+    </row>
+    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A9" t="s">
+        <v>126</v>
+      </c>
+      <c r="B9">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A10" t="s">
+        <v>127</v>
+      </c>
+      <c r="B10">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A11" t="s">
+        <v>115</v>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF6DDD9A-EF34-4108-8532-230729E9C708}">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="8" customWidth="1"/>
-    <col min="2" max="6" width="11.42578125" customWidth="1"/>
-    <col min="7" max="14" width="11.140625" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="5" customWidth="1"/>
+    <col min="2" max="6" width="11.44140625" customWidth="1"/>
+    <col min="7" max="14" width="11.109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>64</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>65</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>60</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>61</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>80</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
       </c>
@@ -5756,8 +5879,8 @@
         <v>134.68</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
       </c>
@@ -5780,8 +5903,8 @@
         <v>271.23</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
       </c>
@@ -5804,8 +5927,8 @@
         <v>53.8</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.124999826388</v>
       </c>
@@ -5828,8 +5951,8 @@
         <v>220.9</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666435187</v>
       </c>
@@ -5852,8 +5975,8 @@
         <v>171.55</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44671.208333043978</v>
       </c>
@@ -5876,8 +5999,8 @@
         <v>397.42</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44671.249999537038</v>
       </c>
@@ -5900,8 +6023,8 @@
         <v>191.92</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44671.291666087964</v>
       </c>
@@ -5924,8 +6047,8 @@
         <v>265.85000000000002</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44671.333332638889</v>
       </c>
@@ -5948,8 +6071,8 @@
         <v>299.97000000000003</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>44671.374999189815</v>
       </c>
@@ -5980,135 +6103,35 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5112C03D-AA3C-4BDB-99A8-E263BCF7A011}">
-  <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{817FDE8F-BC70-48D0-8376-FB52E6946AF1}">
+  <dimension ref="A1:E25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="27" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="10.109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>110</v>
-      </c>
-      <c r="B2">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>111</v>
-      </c>
-      <c r="B3">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" t="s">
-        <v>112</v>
-      </c>
-      <c r="B4">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" t="s">
-        <v>113</v>
-      </c>
-      <c r="B5">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" t="s">
-        <v>114</v>
-      </c>
-      <c r="B6">
-        <v>1</v>
-      </c>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" t="s">
-        <v>116</v>
-      </c>
-      <c r="B7">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" t="s">
-        <v>117</v>
-      </c>
-      <c r="B8">
-        <v>10000</v>
-      </c>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" t="s">
-        <v>126</v>
-      </c>
-      <c r="B9">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" t="s">
-        <v>127</v>
-      </c>
-      <c r="B10">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" t="s">
-        <v>115</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-  <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{817FDE8F-BC70-48D0-8376-FB52E6946AF1}">
-  <dimension ref="A1:E25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.140625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>55</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>56</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>57</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
       </c>
@@ -6129,8 +6152,8 @@
         <v>14.933999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
       </c>
@@ -6151,8 +6174,8 @@
         <v>6.7545000000000002</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
       </c>
@@ -6173,8 +6196,8 @@
         <v>34.6845</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.124999826388</v>
       </c>
@@ -6195,8 +6218,8 @@
         <v>26.847000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666435187</v>
       </c>
@@ -6217,8 +6240,8 @@
         <v>44.735500000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44671.208333043978</v>
       </c>
@@ -6239,8 +6262,8 @@
         <v>31.805999999999994</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44671.249999537038</v>
       </c>
@@ -6261,8 +6284,8 @@
         <v>64.998999999999995</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44671.291666087964</v>
       </c>
@@ -6283,8 +6306,8 @@
         <v>61.474499999999992</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44671.333332638889</v>
       </c>
@@ -6305,8 +6328,8 @@
         <v>9.1009999999999991</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>44671.374999189815</v>
       </c>
@@ -6327,51 +6350,51 @@
         <v>22.486499999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A12" s="8"/>
-    </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A13" s="8"/>
-      <c r="B13" s="3"/>
-      <c r="C13" s="3"/>
-      <c r="D13" s="3"/>
-      <c r="E13" s="3"/>
-    </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A14" s="8"/>
-    </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A15" s="8"/>
-    </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
-      <c r="A16" s="8"/>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="8"/>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="8"/>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="8"/>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="8"/>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="8"/>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="8"/>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="8"/>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="8"/>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="8"/>
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A12" s="5"/>
+    </row>
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A13" s="5"/>
+      <c r="B13" s="2"/>
+      <c r="C13" s="2"/>
+      <c r="D13" s="2"/>
+      <c r="E13" s="2"/>
+    </row>
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A14" s="5"/>
+    </row>
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A15" s="5"/>
+    </row>
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+      <c r="A16" s="5"/>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="5"/>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="5"/>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="5"/>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="5"/>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="5"/>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="5"/>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="5"/>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="5"/>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="5"/>
     </row>
   </sheetData>
   <phoneticPr fontId="1" type="noConversion"/>
@@ -6379,29 +6402,29 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{016E73B5-BC63-43DF-8AE1-9D3A59563F2A}">
   <dimension ref="A1:BA11"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="8" customWidth="1"/>
-    <col min="2" max="3" width="6.5703125" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="5" customWidth="1"/>
+    <col min="2" max="3" width="6.5546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:53" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:53" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
-      <c r="B1" s="7" t="s">
+      <c r="B1" s="4" t="s">
         <v>120</v>
       </c>
-      <c r="C1" s="7" t="s">
+      <c r="C1" s="4" t="s">
         <v>118</v>
       </c>
-      <c r="D1" s="7" t="s">
+      <c r="D1" s="4" t="s">
         <v>119</v>
       </c>
-      <c r="E1" s="7" t="s">
+      <c r="E1" s="4" t="s">
         <v>121</v>
       </c>
       <c r="F1"/>
@@ -6453,8 +6476,8 @@
       <c r="AZ1"/>
       <c r="BA1"/>
     </row>
-    <row r="2" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
+    <row r="2" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
       </c>
@@ -6471,8 +6494,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
+    <row r="3" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
       </c>
@@ -6489,8 +6512,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
+    <row r="4" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
       </c>
@@ -6507,8 +6530,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
+    <row r="5" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.124999826388</v>
       </c>
@@ -6525,8 +6548,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
+    <row r="6" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666435187</v>
       </c>
@@ -6543,8 +6566,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
+    <row r="7" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44671.208333043978</v>
       </c>
@@ -6561,8 +6584,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
+    <row r="8" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44671.249999537038</v>
       </c>
@@ -6579,8 +6602,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
+    <row r="9" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44671.291666087964</v>
       </c>
@@ -6597,8 +6620,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
+    <row r="10" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44671.333332638889</v>
       </c>
@@ -6615,8 +6638,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:53" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
+    <row r="11" spans="1:53" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>44671.374999189815</v>
       </c>
@@ -6630,43 +6653,6 @@
         <v>0</v>
       </c>
       <c r="E11">
-        <v>0</v>
-      </c>
-    </row>
-  </sheetData>
-  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9314D326-256A-435C-AAE3-3517FA836EAE}">
-  <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
-  </cols>
-  <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>47</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>48</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" t="s">
-        <v>49</v>
-      </c>
-      <c r="B2">
-        <v>0.1</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" t="s">
-        <v>50</v>
-      </c>
-      <c r="B3">
         <v>0</v>
       </c>
     </row>
@@ -6676,32 +6662,35 @@
 </file>
 
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A87AD413-E614-48C1-80E1-F1E8236FCBC6}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9314D326-256A-435C-AAE3-3517FA836EAE}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
+  </cols>
   <sheetData>
-    <row r="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>32</v>
-      </c>
-      <c r="B1" s="3" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>47</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>48</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>34</v>
+        <v>49</v>
       </c>
       <c r="B2">
-        <v>0.5</v>
-      </c>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
+        <v>0.1</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
-        <v>35</v>
+        <v>50</v>
       </c>
       <c r="B3">
-        <v>0.5</v>
+        <v>0</v>
       </c>
     </row>
   </sheetData>
@@ -6710,167 +6699,32 @@
 </file>
 
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31679CA5-0AA2-4F6F-8223-14BF74917F04}">
-  <dimension ref="A1:B25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
-  <cols>
-    <col min="1" max="1" width="19.28515625" style="8" customWidth="1"/>
-  </cols>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A87AD413-E614-48C1-80E1-F1E8236FCBC6}">
+  <dimension ref="A1:B3"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:2" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>24</v>
-      </c>
-    </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
-        <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
-        <v>44671</v>
-      </c>
-      <c r="B2" s="2"/>
-    </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
-        <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
-        <v>44671.041666666664</v>
-      </c>
-      <c r="B3" s="2"/>
-    </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
-        <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
-        <v>44671.08333321759</v>
-      </c>
-      <c r="B4" s="2"/>
-    </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
-        <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
-        <v>44671.124999826388</v>
-      </c>
-      <c r="B5" s="2"/>
-    </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
-        <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
-        <v>44671.166666435187</v>
-      </c>
-      <c r="B6" s="2"/>
-    </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
-        <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
-        <v>44671.208333043978</v>
-      </c>
-      <c r="B7" s="2"/>
-    </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
-        <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
-        <v>44671.249999537038</v>
-      </c>
-      <c r="B8" s="2"/>
-    </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
-        <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
-        <v>44671.291666087964</v>
-      </c>
-    </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
-        <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
-        <v>44671.333332638889</v>
-      </c>
-    </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
-        <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
-        <v>44671.374999189815</v>
-      </c>
-    </row>
-    <row r="12" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="str">
-        <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="13" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="str">
-        <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="14" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="str">
-        <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="15" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="str">
-        <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="16" spans="1:2" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="str">
-        <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="str">
-        <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="str">
-        <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="str">
-        <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="8" t="str">
-        <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="str">
-        <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="8" t="str">
-        <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="str">
-        <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="str">
-        <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
-        <v/>
-      </c>
-    </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="str">
-        <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
-        <v/>
+    <row r="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>32</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
+        <v>34</v>
+      </c>
+      <c r="B2">
+        <v>0.5</v>
+      </c>
+    </row>
+    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>35</v>
+      </c>
+      <c r="B3">
+        <v>0.5</v>
       </c>
     </row>
   </sheetData>
@@ -6879,158 +6733,320 @@
 </file>
 
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31679CA5-0AA2-4F6F-8223-14BF74917F04}">
+  <dimension ref="A1:A25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <cols>
+    <col min="1" max="1" width="19.33203125" style="5" customWidth="1"/>
+  </cols>
+  <sheetData>
+    <row r="1" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>24</v>
+      </c>
+    </row>
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
+        <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
+        <v>44671</v>
+      </c>
+    </row>
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
+        <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
+        <v>44671.041666666664</v>
+      </c>
+    </row>
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
+        <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
+        <v>44671.08333321759</v>
+      </c>
+    </row>
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
+        <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
+        <v>44671.124999826388</v>
+      </c>
+    </row>
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
+        <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
+        <v>44671.166666435187</v>
+      </c>
+    </row>
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
+        <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
+        <v>44671.208333043978</v>
+      </c>
+    </row>
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
+        <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
+        <v>44671.249999537038</v>
+      </c>
+    </row>
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
+        <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
+        <v>44671.291666087964</v>
+      </c>
+    </row>
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
+        <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
+        <v>44671.333332638889</v>
+      </c>
+    </row>
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
+        <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
+        <v>44671.374999189815</v>
+      </c>
+    </row>
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="str">
+        <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="str">
+        <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="str">
+        <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="str">
+        <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="str">
+        <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="str">
+        <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="str">
+        <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="str">
+        <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="str">
+        <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="str">
+        <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="5" t="str">
+        <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="5" t="str">
+        <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="5" t="str">
+        <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
+        <v/>
+      </c>
+    </row>
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="5" t="str">
+        <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
+        <v/>
+      </c>
+    </row>
+  </sheetData>
+  <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
+</worksheet>
+</file>
+
+<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD670E02-665B-45B8-BC4E-9596D2C1BC55}">
   <dimension ref="A1:A25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="8" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.124999826388</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666435187</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44671.208333043978</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44671.249999537038</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44671.291666087964</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44671.333332638889</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>44671.374999189815</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="str">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="str">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="str">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="str">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="str">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="str">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="str">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="str">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="8" t="str">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="str">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="8" t="str">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="5" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="str">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="5" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="str">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="5" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="str">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="5" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
       </c>
@@ -7041,159 +7057,159 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7FEDBA5-B0F3-4E9D-9367-08D5F5FA8AEA}">
   <dimension ref="A1:A25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="8" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.124999826388</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666435187</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44671.208333043978</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44671.249999537038</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44671.291666087964</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44671.333332638889</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>44671.374999189815</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="str">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="str">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="str">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="str">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="str">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="str">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="str">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="str">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="8" t="str">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="str">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="8" t="str">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="5" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="str">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="5" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="str">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="5" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="str">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="5" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
       </c>
@@ -7203,17 +7219,17 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5704FC51-737E-45F9-9A9E-85A96AFE5439}">
   <dimension ref="A1:M9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.5703125" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.6640625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>32</v>
       </c>
@@ -7227,7 +7243,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>82</v>
       </c>
@@ -7241,10 +7257,10 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
-      <c r="K9" s="3"/>
-      <c r="L9" s="3"/>
-      <c r="M9" s="3"/>
+    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+      <c r="K9" s="2"/>
+      <c r="L9" s="2"/>
+      <c r="M9" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -7252,19 +7268,19 @@
 </worksheet>
 </file>
 
-<file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
+<file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE12AB76-2BDA-4ACA-A128-8CFB9FB6C8F8}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="8" customWidth="1"/>
-    <col min="2" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="14.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="5.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="5" customWidth="1"/>
+    <col min="2" max="4" width="14.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="14.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="5.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B1" t="s">
@@ -7286,8 +7302,8 @@
         <v>89</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
       </c>
@@ -7310,8 +7326,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
       </c>
@@ -7334,8 +7350,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
       </c>
@@ -7358,8 +7374,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.124999826388</v>
       </c>
@@ -7382,8 +7398,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666435187</v>
       </c>
@@ -7406,8 +7422,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44671.208333043978</v>
       </c>
@@ -7430,8 +7446,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44671.249999537038</v>
       </c>
@@ -7454,8 +7470,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44671.291666087964</v>
       </c>
@@ -7478,8 +7494,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44671.333332638889</v>
       </c>
@@ -7502,8 +7518,8 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>44671.374999189815</v>
       </c>
@@ -7526,86 +7542,86 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="str">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="str">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="str">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="str">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="str">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="str">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="str">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="str">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="8" t="str">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="str">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="8" t="str">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="5" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="str">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="5" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="str">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="5" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="str">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="5" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
       </c>
@@ -7618,216 +7634,216 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04A1B16B-CDA9-46BD-BA51-731AA9327652}">
   <dimension ref="A1:P4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.7109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.140625" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.140625" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.42578125" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.7109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.88671875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.6640625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.44140625" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.6640625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="3" t="s">
+    <row r="1" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
         <v>1</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>6</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>9</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>3</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>101</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>4</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>5</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>52</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="2" t="s">
         <v>109</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="2" t="s">
         <v>102</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="2" t="s">
         <v>123</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="2" t="s">
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>7</v>
       </c>
-      <c r="B2" s="7">
+      <c r="B2" s="4">
         <v>1</v>
       </c>
-      <c r="C2" s="7">
-        <v>0</v>
-      </c>
-      <c r="D2" s="7">
-        <v>0</v>
-      </c>
-      <c r="E2" s="7">
-        <v>0</v>
-      </c>
-      <c r="F2" s="7">
-        <v>0</v>
-      </c>
-      <c r="G2" s="7">
-        <v>0</v>
-      </c>
-      <c r="H2" s="7">
-        <v>0</v>
-      </c>
-      <c r="I2" s="7">
-        <v>0</v>
-      </c>
-      <c r="J2" s="7">
-        <v>0</v>
-      </c>
-      <c r="K2" s="7">
-        <v>0</v>
-      </c>
-      <c r="L2" s="7">
-        <v>0</v>
-      </c>
-      <c r="M2" s="7">
-        <v>0</v>
-      </c>
-      <c r="N2" s="7">
-        <v>0</v>
-      </c>
-      <c r="O2" s="7">
-        <v>0</v>
-      </c>
-      <c r="P2" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="C2" s="4">
+        <v>0</v>
+      </c>
+      <c r="D2" s="4">
+        <v>0</v>
+      </c>
+      <c r="E2" s="4">
+        <v>0</v>
+      </c>
+      <c r="F2" s="4">
+        <v>0</v>
+      </c>
+      <c r="G2" s="4">
+        <v>0</v>
+      </c>
+      <c r="H2" s="4">
+        <v>0</v>
+      </c>
+      <c r="I2" s="4">
+        <v>0</v>
+      </c>
+      <c r="J2" s="4">
+        <v>0</v>
+      </c>
+      <c r="K2" s="4">
+        <v>0</v>
+      </c>
+      <c r="L2" s="4">
+        <v>0</v>
+      </c>
+      <c r="M2" s="4">
+        <v>0</v>
+      </c>
+      <c r="N2" s="4">
+        <v>0</v>
+      </c>
+      <c r="O2" s="4">
+        <v>0</v>
+      </c>
+      <c r="P2" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>8</v>
       </c>
-      <c r="B3" s="7">
-        <v>0</v>
-      </c>
-      <c r="C3" s="7">
-        <v>0</v>
-      </c>
-      <c r="D3" s="7">
+      <c r="B3" s="4">
+        <v>0</v>
+      </c>
+      <c r="C3" s="4">
+        <v>0</v>
+      </c>
+      <c r="D3" s="4">
         <v>1</v>
       </c>
-      <c r="E3" s="7">
-        <v>0</v>
-      </c>
-      <c r="F3" s="7">
-        <v>0</v>
-      </c>
-      <c r="G3" s="7">
-        <v>0</v>
-      </c>
-      <c r="H3" s="7">
-        <v>0</v>
-      </c>
-      <c r="I3" s="7">
-        <v>0</v>
-      </c>
-      <c r="J3" s="7">
-        <v>0</v>
-      </c>
-      <c r="K3" s="7">
-        <v>0</v>
-      </c>
-      <c r="L3" s="7">
-        <v>0</v>
-      </c>
-      <c r="M3" s="7">
-        <v>0</v>
-      </c>
-      <c r="N3" s="7">
-        <v>0</v>
-      </c>
-      <c r="O3" s="7">
-        <v>0</v>
-      </c>
-      <c r="P3" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
+      <c r="E3" s="4">
+        <v>0</v>
+      </c>
+      <c r="F3" s="4">
+        <v>0</v>
+      </c>
+      <c r="G3" s="4">
+        <v>0</v>
+      </c>
+      <c r="H3" s="4">
+        <v>0</v>
+      </c>
+      <c r="I3" s="4">
+        <v>0</v>
+      </c>
+      <c r="J3" s="4">
+        <v>0</v>
+      </c>
+      <c r="K3" s="4">
+        <v>0</v>
+      </c>
+      <c r="L3" s="4">
+        <v>0</v>
+      </c>
+      <c r="M3" s="4">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0</v>
+      </c>
+      <c r="O3" s="4">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>70</v>
       </c>
-      <c r="B4" s="7">
-        <v>0</v>
-      </c>
-      <c r="C4" s="7">
-        <v>0</v>
-      </c>
-      <c r="D4" s="7">
-        <v>0</v>
-      </c>
-      <c r="E4" s="7">
-        <v>0</v>
-      </c>
-      <c r="F4" s="7">
+      <c r="B4" s="4">
+        <v>0</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0</v>
+      </c>
+      <c r="E4" s="4">
+        <v>0</v>
+      </c>
+      <c r="F4" s="4">
         <v>1</v>
       </c>
-      <c r="G4" s="7">
-        <v>0</v>
-      </c>
-      <c r="H4" s="7">
-        <v>0</v>
-      </c>
-      <c r="I4" s="7">
-        <v>0</v>
-      </c>
-      <c r="J4" s="7">
-        <v>0</v>
-      </c>
-      <c r="K4" s="7">
-        <v>0</v>
-      </c>
-      <c r="L4" s="7">
-        <v>0</v>
-      </c>
-      <c r="M4" s="7">
-        <v>0</v>
-      </c>
-      <c r="N4" s="7">
-        <v>0</v>
-      </c>
-      <c r="O4" s="7">
-        <v>0</v>
-      </c>
-      <c r="P4" s="7">
+      <c r="G4" s="4">
+        <v>0</v>
+      </c>
+      <c r="H4" s="4">
+        <v>0</v>
+      </c>
+      <c r="I4" s="4">
+        <v>0</v>
+      </c>
+      <c r="J4" s="4">
+        <v>0</v>
+      </c>
+      <c r="K4" s="4">
+        <v>0</v>
+      </c>
+      <c r="L4" s="4">
+        <v>0</v>
+      </c>
+      <c r="M4" s="4">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0</v>
+      </c>
+      <c r="O4" s="4">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4">
         <v>0</v>
       </c>
     </row>
@@ -7839,235 +7855,235 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB20090B-02A9-43B7-8D03-9C18D42920EB}">
   <dimension ref="A1:Q9"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.88671875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.140625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.7109375" customWidth="1"/>
+    <col min="3" max="3" width="8.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.6640625" customWidth="1"/>
     <col min="7" max="7" width="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.28515625" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="9.5703125" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.140625" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.42578125" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="11.42578125" customWidth="1"/>
+    <col min="8" max="8" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="9.5546875" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="11.44140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>12</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>44</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>13</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>26</v>
       </c>
-      <c r="F1" s="3" t="s">
+      <c r="F1" s="2" t="s">
         <v>16</v>
       </c>
-      <c r="G1" s="3" t="s">
+      <c r="G1" s="2" t="s">
         <v>15</v>
       </c>
-      <c r="H1" s="3" t="s">
+      <c r="H1" s="2" t="s">
         <v>18</v>
       </c>
-      <c r="I1" s="3" t="s">
+      <c r="I1" s="2" t="s">
         <v>17</v>
       </c>
-      <c r="J1" s="3" t="s">
+      <c r="J1" s="2" t="s">
         <v>36</v>
       </c>
-      <c r="K1" s="3" t="s">
+      <c r="K1" s="2" t="s">
         <v>38</v>
       </c>
-      <c r="L1" s="3" t="s">
+      <c r="L1" s="2" t="s">
         <v>39</v>
       </c>
-      <c r="M1" s="3" t="s">
+      <c r="M1" s="2" t="s">
         <v>66</v>
       </c>
-      <c r="N1" s="3" t="s">
+      <c r="N1" s="2" t="s">
         <v>67</v>
       </c>
-      <c r="O1" s="3" t="s">
+      <c r="O1" s="2" t="s">
         <v>45</v>
       </c>
-      <c r="P1" s="3" t="s">
+      <c r="P1" s="2" t="s">
         <v>108</v>
       </c>
-      <c r="Q1" s="3" t="s">
+      <c r="Q1" s="2" t="s">
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>71</v>
       </c>
-      <c r="B2" s="7">
-        <v>0</v>
-      </c>
-      <c r="C2" s="7">
-        <v>0</v>
-      </c>
-      <c r="D2" s="7">
+      <c r="B2" s="4">
+        <v>0</v>
+      </c>
+      <c r="C2" s="4">
+        <v>0</v>
+      </c>
+      <c r="D2" s="4">
         <v>1</v>
       </c>
-      <c r="E2" s="7">
+      <c r="E2" s="4">
         <v>1</v>
       </c>
-      <c r="F2" s="7">
+      <c r="F2" s="4">
         <v>1</v>
       </c>
-      <c r="G2" s="7">
+      <c r="G2" s="4">
         <v>0.9</v>
       </c>
-      <c r="H2" s="7">
+      <c r="H2" s="4">
         <v>0.3</v>
       </c>
-      <c r="I2" s="7">
+      <c r="I2" s="4">
         <v>1</v>
       </c>
-      <c r="J2" s="7">
+      <c r="J2" s="4">
         <v>1</v>
       </c>
-      <c r="K2" s="7">
+      <c r="K2" s="4">
         <v>2</v>
       </c>
-      <c r="L2" s="7">
+      <c r="L2" s="4">
         <v>2</v>
       </c>
-      <c r="M2" s="7">
-        <v>0</v>
-      </c>
-      <c r="N2" s="7">
-        <v>0</v>
-      </c>
-      <c r="O2" s="7">
+      <c r="M2" s="4">
+        <v>0</v>
+      </c>
+      <c r="N2" s="4">
+        <v>0</v>
+      </c>
+      <c r="O2" s="4">
         <v>1</v>
       </c>
-      <c r="P2" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q2" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="P2" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q2" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>73</v>
       </c>
-      <c r="B3" s="7">
+      <c r="B3" s="4">
         <v>1</v>
       </c>
-      <c r="C3" s="7">
-        <v>0</v>
-      </c>
-      <c r="D3" s="7">
-        <v>0</v>
-      </c>
-      <c r="E3" s="7">
-        <v>0</v>
-      </c>
-      <c r="F3" s="7">
+      <c r="C3" s="4">
+        <v>0</v>
+      </c>
+      <c r="D3" s="4">
+        <v>0</v>
+      </c>
+      <c r="E3" s="4">
+        <v>0</v>
+      </c>
+      <c r="F3" s="4">
         <v>1</v>
       </c>
-      <c r="G3" s="7">
+      <c r="G3" s="4">
         <v>1</v>
       </c>
-      <c r="H3" s="7">
-        <v>0</v>
-      </c>
-      <c r="I3" s="7">
+      <c r="H3" s="4">
+        <v>0</v>
+      </c>
+      <c r="I3" s="4">
         <v>1</v>
       </c>
-      <c r="J3" s="7">
-        <v>0</v>
-      </c>
-      <c r="K3" s="7">
-        <v>0</v>
-      </c>
-      <c r="L3" s="7">
-        <v>0</v>
-      </c>
-      <c r="M3" s="7">
-        <v>0</v>
-      </c>
-      <c r="N3" s="7">
-        <v>0</v>
-      </c>
-      <c r="O3" s="7">
-        <v>0</v>
-      </c>
-      <c r="P3" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q3" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
+      <c r="J3" s="4">
+        <v>0</v>
+      </c>
+      <c r="K3" s="4">
+        <v>0</v>
+      </c>
+      <c r="L3" s="4">
+        <v>0</v>
+      </c>
+      <c r="M3" s="4">
+        <v>0</v>
+      </c>
+      <c r="N3" s="4">
+        <v>0</v>
+      </c>
+      <c r="O3" s="4">
+        <v>0</v>
+      </c>
+      <c r="P3" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q3" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>72</v>
       </c>
-      <c r="B4" s="7">
-        <v>0</v>
-      </c>
-      <c r="C4" s="7">
-        <v>0</v>
-      </c>
-      <c r="D4" s="7">
-        <v>0</v>
-      </c>
-      <c r="E4" s="7">
+      <c r="B4" s="4">
+        <v>0</v>
+      </c>
+      <c r="C4" s="4">
+        <v>0</v>
+      </c>
+      <c r="D4" s="4">
+        <v>0</v>
+      </c>
+      <c r="E4" s="4">
         <v>1</v>
       </c>
-      <c r="F4" s="7">
+      <c r="F4" s="4">
         <v>1</v>
       </c>
-      <c r="G4" s="7">
+      <c r="G4" s="4">
         <v>3</v>
       </c>
-      <c r="H4" s="7">
-        <v>0</v>
-      </c>
-      <c r="I4" s="7">
+      <c r="H4" s="4">
+        <v>0</v>
+      </c>
+      <c r="I4" s="4">
         <v>1</v>
       </c>
-      <c r="J4" s="7">
-        <v>0</v>
-      </c>
-      <c r="K4" s="7">
-        <v>0</v>
-      </c>
-      <c r="L4" s="7">
-        <v>0</v>
-      </c>
-      <c r="M4" s="7">
-        <v>0</v>
-      </c>
-      <c r="N4" s="7">
-        <v>0</v>
-      </c>
-      <c r="O4" s="7">
-        <v>0</v>
-      </c>
-      <c r="P4" s="7">
-        <v>0</v>
-      </c>
-      <c r="Q4" s="7">
-        <v>0</v>
-      </c>
-    </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
-      <c r="Q9" s="3"/>
+      <c r="J4" s="4">
+        <v>0</v>
+      </c>
+      <c r="K4" s="4">
+        <v>0</v>
+      </c>
+      <c r="L4" s="4">
+        <v>0</v>
+      </c>
+      <c r="M4" s="4">
+        <v>0</v>
+      </c>
+      <c r="N4" s="4">
+        <v>0</v>
+      </c>
+      <c r="O4" s="4">
+        <v>0</v>
+      </c>
+      <c r="P4" s="4">
+        <v>0</v>
+      </c>
+      <c r="Q4" s="4">
+        <v>0</v>
+      </c>
+    </row>
+    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+      <c r="Q9" s="2"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8077,20 +8093,20 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5539A729-4FB7-440D-A765-676495DE3453}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>125</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>68</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>69</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -8101,7 +8117,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -8112,7 +8128,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -8131,48 +8147,48 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAB1106B-D567-41FC-8E91-2B4CC5EC9B59}">
   <dimension ref="A1:K1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <sheetData>
-    <row r="1" spans="1:11" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="3">
+      <c r="B1" s="2">
         <v>1</v>
       </c>
-      <c r="C1" s="3">
+      <c r="C1" s="2">
         <f>B1+1</f>
         <v>2</v>
       </c>
-      <c r="D1" s="3">
+      <c r="D1" s="2">
         <f t="shared" ref="D1:K1" si="0">C1+1</f>
         <v>3</v>
       </c>
-      <c r="E1" s="3">
+      <c r="E1" s="2">
         <f t="shared" si="0"/>
         <v>4</v>
       </c>
-      <c r="F1" s="3">
+      <c r="F1" s="2">
         <f t="shared" si="0"/>
         <v>5</v>
       </c>
-      <c r="G1" s="3">
+      <c r="G1" s="2">
         <f t="shared" si="0"/>
         <v>6</v>
       </c>
-      <c r="H1" s="3">
+      <c r="H1" s="2">
         <f t="shared" si="0"/>
         <v>7</v>
       </c>
-      <c r="I1" s="3">
+      <c r="I1" s="2">
         <f t="shared" si="0"/>
         <v>8</v>
       </c>
-      <c r="J1" s="3">
+      <c r="J1" s="2">
         <f t="shared" si="0"/>
         <v>9</v>
       </c>
-      <c r="K1" s="3">
+      <c r="K1" s="2">
         <f t="shared" si="0"/>
         <v>10</v>
       </c>
@@ -8184,249 +8200,242 @@
 
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A86A8A7-FD76-4891-A53C-CBB095359118}">
-  <dimension ref="A1:J9"/>
-  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <dimension ref="A1:J7"/>
+  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="16.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.42578125" style="5" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.140625" style="5" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.85546875" style="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5703125" style="5" bestFit="1" customWidth="1"/>
-    <col min="9" max="16384" width="9.140625" style="5"/>
+    <col min="1" max="1" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.44140625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.44140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.88671875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="4" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="4" t="s">
+    <row r="1" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
-      <c r="B1" s="4" t="s">
+      <c r="B1" s="2" t="s">
         <v>22</v>
       </c>
-      <c r="C1" s="4" t="s">
-        <v>0</v>
-      </c>
-      <c r="D1" s="4" t="s">
+      <c r="C1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="D1" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="E1" s="4" t="s">
+      <c r="E1" s="2" t="s">
         <v>14</v>
       </c>
-      <c r="F1" s="4" t="s">
+      <c r="F1" s="2" t="s">
         <v>122</v>
       </c>
-      <c r="G1" s="4" t="s">
+      <c r="G1" s="2" t="s">
         <v>20</v>
       </c>
-      <c r="H1" s="4" t="s">
+      <c r="H1" s="2" t="s">
         <v>19</v>
       </c>
-      <c r="I1" s="4" t="s">
+      <c r="I1" s="2" t="s">
         <v>107</v>
       </c>
-      <c r="J1" s="4" t="s">
+      <c r="J1" s="2" t="s">
         <v>106</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A2" s="5" t="s">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>71</v>
       </c>
-      <c r="B2" s="5" t="s">
+      <c r="B2" t="s">
         <v>21</v>
       </c>
-      <c r="C2" s="5" t="s">
+      <c r="C2" t="s">
         <v>7</v>
       </c>
-      <c r="D2" s="5">
+      <c r="D2">
         <v>1</v>
       </c>
-      <c r="E2" s="5">
+      <c r="E2">
         <v>10</v>
       </c>
-      <c r="F2" s="5">
-        <v>0</v>
-      </c>
-      <c r="G2" s="5">
+      <c r="F2">
+        <v>0</v>
+      </c>
+      <c r="G2">
         <v>1</v>
       </c>
-      <c r="H2" s="5">
+      <c r="H2">
         <v>1</v>
       </c>
-      <c r="I2" s="5">
+      <c r="I2">
         <v>0.7</v>
       </c>
-      <c r="J2" s="5">
+      <c r="J2">
         <v>0.7</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A3" s="5" t="s">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
         <v>71</v>
       </c>
-      <c r="B3" s="5" t="s">
+      <c r="B3" t="s">
         <v>23</v>
       </c>
-      <c r="C3" s="5" t="s">
+      <c r="C3" t="s">
         <v>8</v>
       </c>
-      <c r="D3" s="5">
+      <c r="D3">
         <v>1</v>
       </c>
-      <c r="E3" s="5">
+      <c r="E3">
         <v>3</v>
       </c>
-      <c r="F3" s="5">
-        <v>0</v>
-      </c>
-      <c r="G3" s="5">
+      <c r="F3">
+        <v>0</v>
+      </c>
+      <c r="G3">
         <v>1</v>
       </c>
-      <c r="H3" s="5">
+      <c r="H3">
         <v>1</v>
       </c>
-      <c r="I3" s="5">
+      <c r="I3">
         <v>0.7</v>
       </c>
-      <c r="J3" s="5">
+      <c r="J3">
         <v>0.7</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A4" s="5" t="s">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A4" t="s">
         <v>71</v>
       </c>
-      <c r="B4" s="5" t="s">
+      <c r="B4" t="s">
         <v>23</v>
       </c>
-      <c r="C4" s="5" t="s">
+      <c r="C4" t="s">
         <v>70</v>
       </c>
-      <c r="D4" s="5">
+      <c r="D4">
         <v>1</v>
       </c>
-      <c r="E4" s="5">
+      <c r="E4">
         <v>6</v>
       </c>
-      <c r="F4" s="5">
-        <v>0</v>
-      </c>
-      <c r="G4" s="5">
+      <c r="F4">
+        <v>0</v>
+      </c>
+      <c r="G4">
         <v>1</v>
       </c>
-      <c r="H4" s="5">
+      <c r="H4">
         <v>1</v>
       </c>
-      <c r="I4" s="5">
+      <c r="I4">
         <v>0.7</v>
       </c>
-      <c r="J4" s="5">
+      <c r="J4">
         <v>0.7</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A5" s="5" t="s">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+      <c r="A5" t="s">
         <v>73</v>
       </c>
-      <c r="B5" s="5" t="s">
+      <c r="B5" t="s">
         <v>23</v>
       </c>
-      <c r="C5" s="5" t="s">
+      <c r="C5" t="s">
         <v>8</v>
       </c>
-      <c r="D5" s="5">
+      <c r="D5">
         <v>1</v>
       </c>
-      <c r="E5" s="5">
+      <c r="E5">
         <v>5</v>
       </c>
-      <c r="F5" s="5">
-        <v>0</v>
-      </c>
-      <c r="G5" s="5">
+      <c r="F5">
+        <v>0</v>
+      </c>
+      <c r="G5">
         <v>1</v>
       </c>
-      <c r="H5" s="5">
+      <c r="H5">
         <v>1</v>
       </c>
-      <c r="I5" s="5">
+      <c r="I5">
         <v>0.7</v>
       </c>
-      <c r="J5" s="5">
+      <c r="J5">
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A6" t="s">
         <v>72</v>
       </c>
-      <c r="B6" s="5" t="s">
+      <c r="B6" t="s">
         <v>21</v>
       </c>
-      <c r="C6" s="5" t="s">
+      <c r="C6" t="s">
         <v>8</v>
       </c>
-      <c r="D6" s="5">
+      <c r="D6">
         <v>1</v>
       </c>
-      <c r="E6" s="5">
+      <c r="E6">
         <v>3</v>
       </c>
-      <c r="F6" s="5">
-        <v>0</v>
-      </c>
-      <c r="G6" s="5">
+      <c r="F6">
+        <v>0</v>
+      </c>
+      <c r="G6">
         <v>5</v>
       </c>
-      <c r="H6" s="5">
+      <c r="H6">
         <v>5</v>
       </c>
-      <c r="I6" s="5">
+      <c r="I6">
         <v>0.7</v>
       </c>
-      <c r="J6" s="5">
+      <c r="J6">
         <v>0.7</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
       <c r="A7" t="s">
         <v>72</v>
       </c>
-      <c r="B7" s="5" t="s">
+      <c r="B7" t="s">
         <v>23</v>
       </c>
-      <c r="C7" s="5" t="s">
+      <c r="C7" t="s">
         <v>70</v>
       </c>
-      <c r="D7" s="5">
+      <c r="D7">
         <v>1</v>
       </c>
-      <c r="E7" s="5">
+      <c r="E7">
         <v>9</v>
       </c>
-      <c r="F7" s="5">
-        <v>0</v>
-      </c>
-      <c r="G7" s="5">
+      <c r="F7">
+        <v>0</v>
+      </c>
+      <c r="G7">
         <v>5</v>
       </c>
-      <c r="H7" s="5">
+      <c r="H7">
         <v>5</v>
       </c>
-      <c r="I7" s="5">
+      <c r="I7">
         <v>0.7</v>
       </c>
-      <c r="J7" s="5">
+      <c r="J7">
         <v>0.7</v>
       </c>
-    </row>
-    <row r="8" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A8"/>
-    </row>
-    <row r="9" spans="1:10" x14ac:dyDescent="0.25">
-      <c r="A9"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -8437,156 +8446,156 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7AEF404-3743-47D7-AC45-7AE3A9FB796E}">
   <dimension ref="A1:A25"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="19.28515625" style="8" customWidth="1"/>
+    <col min="1" max="1" width="19.33203125" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A2" s="8">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A2" s="5">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A3" s="8">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A3" s="5">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A4" s="8">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A4" s="5">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A5" s="8">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A5" s="5">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.124999826388</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A6" s="8">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A6" s="5">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666435187</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A7" s="8">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A7" s="5">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44671.208333043978</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A8" s="8">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A8" s="5">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44671.249999537038</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A9" s="8">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A9" s="5">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44671.291666087964</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A10" s="8">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A10" s="5">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44671.333332638889</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A11" s="8">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A11" s="5">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>44671.374999189815</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A12" s="8" t="str">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A12" s="5" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A13" s="8" t="str">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A13" s="5" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A14" s="8" t="str">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A14" s="5" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A15" s="8" t="str">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A15" s="5" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A16" s="8" t="str">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A16" s="5" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A17" s="8" t="str">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A17" s="5" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A18" s="8" t="str">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A18" s="5" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A19" s="8" t="str">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A19" s="5" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A20" s="8" t="str">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A20" s="5" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A21" s="8" t="str">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A21" s="5" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A22" s="8" t="str">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A22" s="5" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A23" s="8" t="str">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A23" s="5" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A24" s="8" t="str">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A24" s="5" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
-      <c r="A25" s="8" t="str">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+      <c r="A25" s="5" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
       </c>
@@ -8599,27 +8608,27 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{596E3FE2-967D-4C0B-BDAC-EF3704EC4DDF}">
   <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="2" width="6.28515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.28515625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="6.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.33203125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.33203125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="3" customFormat="1" x14ac:dyDescent="0.25">
-      <c r="A1" s="3" t="s">
+    <row r="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+      <c r="A1" s="2" t="s">
         <v>99</v>
       </c>
-      <c r="B1" s="3" t="s">
+      <c r="B1" s="2" t="s">
         <v>100</v>
       </c>
-      <c r="C1" s="3" t="s">
+      <c r="C1" s="2" t="s">
         <v>103</v>
       </c>
-      <c r="D1" s="3" t="s">
+      <c r="D1" s="2" t="s">
         <v>104</v>
       </c>
-      <c r="E1" s="3" t="s">
+      <c r="E1" s="2" t="s">
         <v>105</v>
       </c>
     </row>

--- a/input_data/example_model.xlsx
+++ b/input_data/example_model.xlsx
@@ -1,14 +1,14 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28526"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dsdennis\HOPE\Predicer\input_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{01DF83F7-EE22-422F-A6C0-4C829A97F6A4}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB1E369B-DE44-49F1-B2B3-4E4815D840DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="796" firstSheet="4" activeTab="14" xr2:uid="{788BFBD1-D930-4535-8A91-D85C56924796}"/>
   </bookViews>
@@ -61,7 +61,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="196" uniqueCount="133">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="197" uniqueCount="134">
   <si>
     <t>node</t>
   </si>
@@ -460,6 +460,9 @@
   </si>
   <si>
     <t>inflow</t>
+  </si>
+  <si>
+    <t>deviation_penalty</t>
   </si>
 </sst>
 </file>
@@ -4995,13 +4998,13 @@
 
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBF5682F-29D1-41D2-B323-E6C39BD83827}">
-  <dimension ref="A1:F1"/>
+  <dimension ref="A1:G1"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
         <v>128</v>
       </c>
@@ -5019,6 +5022,9 @@
       </c>
       <c r="F1" t="s">
         <v>132</v>
+      </c>
+      <c r="G1" t="s">
+        <v>133</v>
       </c>
     </row>
   </sheetData>

--- a/input_data/example_model.xlsx
+++ b/input_data/example_model.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29029"/>
   <workbookPr defaultThemeVersion="166925"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\dsdennis\HOPE\Predicer\input_data\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{DB1E369B-DE44-49F1-B2B3-4E4815D840DD}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{18FA550F-C30C-4176-B5D0-6395170E33EC}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12576" tabRatio="796" firstSheet="4" activeTab="14" xr2:uid="{788BFBD1-D930-4535-8A91-D85C56924796}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="17520" tabRatio="796" firstSheet="4" activeTab="16" xr2:uid="{788BFBD1-D930-4535-8A91-D85C56924796}"/>
   </bookViews>
   <sheets>
     <sheet name="timeseries" sheetId="18" r:id="rId1"/>
@@ -660,7 +660,7 @@
             <c:numRef>
               <c:f>cf!$A$2:$A$11</c:f>
               <c:numCache>
-                <c:formatCode>d:m:yyyy\ h\:mm;@</c:formatCode>
+                <c:formatCode>d/m/yyyy\ h\:mm;@</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>44671</c:v>
@@ -783,7 +783,7 @@
             <c:numRef>
               <c:f>cf!$A$2:$A$11</c:f>
               <c:numCache>
-                <c:formatCode>d:m:yyyy\ h\:mm;@</c:formatCode>
+                <c:formatCode>d/m/yyyy\ h\:mm;@</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>44671</c:v>
@@ -1157,6 +1157,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1164,7 +1165,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1331,7 +1331,7 @@
             <c:numRef>
               <c:f>market_prices!$A$2:$A$11</c:f>
               <c:numCache>
-                <c:formatCode>d:m:yyyy\ h\:mm;@</c:formatCode>
+                <c:formatCode>d/m/yyyy\ h\:mm;@</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>44671</c:v>
@@ -1454,7 +1454,7 @@
             <c:numRef>
               <c:f>market_prices!$A$2:$A$11</c:f>
               <c:numCache>
-                <c:formatCode>d:m:yyyy\ h\:mm;@</c:formatCode>
+                <c:formatCode>d/m/yyyy\ h\:mm;@</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>44671</c:v>
@@ -1623,7 +1623,7 @@
             </a:p>
           </c:txPr>
         </c:title>
-        <c:numFmt formatCode="d:m:yyyy\ h\:mm;@" sourceLinked="1"/>
+        <c:numFmt formatCode="d/m/yyyy\ h\:mm;@" sourceLinked="1"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -1823,6 +1823,7 @@
     </c:legend>
     <c:plotVisOnly val="1"/>
     <c:dispBlanksAs val="gap"/>
+    <c:showDLblsOverMax val="0"/>
     <c:extLst>
       <c:ext xmlns:c16r3="http://schemas.microsoft.com/office/drawing/2017/03/chart" uri="{56B9EC1D-385E-4148-901F-78D8002777C0}">
         <c16r3:dataDisplayOptions16>
@@ -1830,7 +1831,6 @@
         </c16r3:dataDisplayOptions16>
       </c:ext>
     </c:extLst>
-    <c:showDLblsOverMax val="0"/>
   </c:chart>
   <c:spPr>
     <a:solidFill>
@@ -1953,7 +1953,7 @@
             <c:numRef>
               <c:f>market_prices!$A$2:$A$11</c:f>
               <c:numCache>
-                <c:formatCode>d:m:yyyy\ h\:mm;@</c:formatCode>
+                <c:formatCode>d/m/yyyy\ h\:mm;@</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>44671</c:v>
@@ -2052,7 +2052,7 @@
             <c:numRef>
               <c:f>market_prices!$A$2:$A$11</c:f>
               <c:numCache>
-                <c:formatCode>d:m:yyyy\ h\:mm;@</c:formatCode>
+                <c:formatCode>d/m/yyyy\ h\:mm;@</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>44671</c:v>
@@ -2151,7 +2151,7 @@
             <c:numRef>
               <c:f>market_prices!$A$2:$A$11</c:f>
               <c:numCache>
-                <c:formatCode>d:m:yyyy\ h\:mm;@</c:formatCode>
+                <c:formatCode>d/m/yyyy\ h\:mm;@</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>44671</c:v>
@@ -2250,7 +2250,7 @@
             <c:numRef>
               <c:f>market_prices!$A$2:$A$11</c:f>
               <c:numCache>
-                <c:formatCode>d:m:yyyy\ h\:mm;@</c:formatCode>
+                <c:formatCode>d/m/yyyy\ h\:mm;@</c:formatCode>
                 <c:ptCount val="10"/>
                 <c:pt idx="0">
                   <c:v>44671</c:v>
@@ -2399,7 +2399,7 @@
             <a:effectLst/>
           </c:spPr>
         </c:title>
-        <c:numFmt formatCode="d:m:yyyy\ h\:mm;@" sourceLinked="1"/>
+        <c:numFmt formatCode="d/m/yyyy\ h\:mm;@" sourceLinked="1"/>
         <c:majorTickMark val="out"/>
         <c:minorTickMark val="none"/>
         <c:tickLblPos val="nextTo"/>
@@ -4128,178 +4128,178 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{39053E69-3A75-490E-847C-66A9CF6C1FC5}">
   <dimension ref="A1:A49"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <v>44671</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <v>44671.041666666664</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>44671.08333321759</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>44671.124999826388</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>44671.166666435187</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>44671.208333043978</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>44671.249999537038</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>44671.291666087964</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>44671.333332638889</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>44671.374999189815</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="5"/>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="5"/>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="5"/>
     </row>
-    <row r="26" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="26" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A26" s="5"/>
     </row>
-    <row r="27" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="27" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A27" s="5"/>
     </row>
-    <row r="28" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="28" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A28" s="5"/>
     </row>
-    <row r="29" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="29" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A29" s="5"/>
     </row>
-    <row r="30" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="30" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A30" s="5"/>
     </row>
-    <row r="31" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="31" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A31" s="5"/>
     </row>
-    <row r="32" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="32" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A32" s="5"/>
     </row>
-    <row r="33" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="33" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A33" s="5"/>
     </row>
-    <row r="34" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="34" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A34" s="5"/>
     </row>
-    <row r="35" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="35" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A35" s="5"/>
     </row>
-    <row r="36" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="36" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A36" s="5"/>
     </row>
-    <row r="37" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="37" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A37" s="5"/>
     </row>
-    <row r="38" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="38" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A38" s="5"/>
     </row>
-    <row r="39" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="39" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A39" s="5"/>
     </row>
-    <row r="40" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="40" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A40" s="5"/>
     </row>
-    <row r="41" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="41" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A41" s="5"/>
     </row>
-    <row r="42" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="42" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A42" s="5"/>
     </row>
-    <row r="43" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="43" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A43" s="5"/>
     </row>
-    <row r="44" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="44" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A44" s="5"/>
     </row>
-    <row r="45" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="45" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A45" s="5"/>
     </row>
-    <row r="46" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="46" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A46" s="5"/>
     </row>
-    <row r="47" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="47" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A47" s="5"/>
     </row>
-    <row r="48" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="48" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A48" s="5"/>
     </row>
-    <row r="49" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="49" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A49" s="5"/>
     </row>
   </sheetData>
@@ -4311,73 +4311,73 @@
 <file path=xl/worksheets/sheet10.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E8F1FEF7-A337-4ADD-8F2A-03D982D23844}">
   <dimension ref="A1:C11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" style="5" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
       <c r="B1" s="2"/>
       <c r="C1" s="2"/>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.124999826388</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666435187</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44671.208333043978</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44671.249999537038</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44671.291666087964</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44671.333332638889</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>44671.374999189815</v>
@@ -4392,9 +4392,9 @@
 <file path=xl/worksheets/sheet11.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{F0532F8A-0FB4-47AD-98A1-4065D3376432}">
   <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>42</v>
       </c>
@@ -4402,7 +4402,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>41</v>
       </c>
@@ -4418,15 +4418,15 @@
 <file path=xl/worksheets/sheet12.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{77A4637A-7829-48D6-AE54-2E654AB1A427}">
   <dimension ref="A1:L25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" style="5" customWidth="1"/>
-    <col min="2" max="5" width="12.5546875" bestFit="1" customWidth="1"/>
-    <col min="6" max="8" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="12.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" style="5" customWidth="1"/>
+    <col min="2" max="5" width="12.5703125" bestFit="1" customWidth="1"/>
+    <col min="6" max="8" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="12.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
@@ -4437,7 +4437,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
@@ -4451,7 +4451,7 @@
       <c r="F2" s="5"/>
       <c r="L2" s="5"/>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
@@ -4463,7 +4463,7 @@
         <v>0.52</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
@@ -4475,7 +4475,7 @@
         <v>0.56000000000000005</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.124999826388</v>
@@ -4487,7 +4487,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666435187</v>
@@ -4499,7 +4499,7 @@
         <v>0.33</v>
       </c>
     </row>
-    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44671.208333043978</v>
@@ -4511,7 +4511,7 @@
         <v>0.45</v>
       </c>
     </row>
-    <row r="8" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44671.249999537038</v>
@@ -4523,7 +4523,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="9" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44671.291666087964</v>
@@ -4535,7 +4535,7 @@
         <v>0.47</v>
       </c>
     </row>
-    <row r="10" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44671.333332638889</v>
@@ -4547,7 +4547,7 @@
         <v>0.39</v>
       </c>
     </row>
-    <row r="11" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>44671.374999189815</v>
@@ -4559,85 +4559,85 @@
         <v>0.27</v>
       </c>
     </row>
-    <row r="12" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
@@ -4654,14 +4654,14 @@
 <file path=xl/worksheets/sheet13.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{1F87DD44-A1AD-4241-AED7-C48CC9DEE2E2}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" style="5" customWidth="1"/>
-    <col min="4" max="6" width="10.44140625" customWidth="1"/>
-    <col min="7" max="7" width="10.44140625" style="1" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" style="5" customWidth="1"/>
+    <col min="4" max="6" width="10.42578125" customWidth="1"/>
+    <col min="7" max="7" width="10.42578125" style="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
@@ -4672,7 +4672,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
@@ -4685,7 +4685,7 @@
       </c>
       <c r="G2"/>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
@@ -4698,7 +4698,7 @@
       </c>
       <c r="G3"/>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
@@ -4711,7 +4711,7 @@
       </c>
       <c r="G4"/>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.124999826388</v>
@@ -4724,7 +4724,7 @@
       </c>
       <c r="G5"/>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666435187</v>
@@ -4737,7 +4737,7 @@
       </c>
       <c r="G6"/>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44671.208333043978</v>
@@ -4750,7 +4750,7 @@
       </c>
       <c r="G7"/>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44671.249999537038</v>
@@ -4763,7 +4763,7 @@
       </c>
       <c r="G8"/>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44671.291666087964</v>
@@ -4776,7 +4776,7 @@
       </c>
       <c r="G9"/>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44671.333332638889</v>
@@ -4789,7 +4789,7 @@
       </c>
       <c r="G10"/>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>44671.374999189815</v>
@@ -4802,98 +4802,98 @@
       </c>
       <c r="G11"/>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
       <c r="G12"/>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
       <c r="G13"/>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
       <c r="G14"/>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
       <c r="G15"/>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
       <c r="G16"/>
     </row>
-    <row r="17" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
       <c r="G17"/>
     </row>
-    <row r="18" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
       <c r="G18"/>
     </row>
-    <row r="19" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
       <c r="G19"/>
     </row>
-    <row r="20" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
       <c r="G20"/>
     </row>
-    <row r="21" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
       <c r="G21"/>
     </row>
-    <row r="22" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
       <c r="G22"/>
     </row>
-    <row r="23" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
       <c r="G23"/>
     </row>
-    <row r="24" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
       <c r="G24"/>
     </row>
-    <row r="25" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
@@ -4910,82 +4910,82 @@
 <file path=xl/worksheets/sheet14.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{E44A96C9-CA4B-4735-AF1E-65BD86DB3657}">
   <dimension ref="A1:F17"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="3" max="6" width="13.33203125" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="13.6640625" customWidth="1"/>
+    <col min="3" max="6" width="13.28515625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="13.7109375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A2">
         <v>1</v>
       </c>
       <c r="C2" s="5"/>
       <c r="E2" s="5"/>
     </row>
-    <row r="3" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A3">
         <v>2</v>
       </c>
       <c r="C3" s="5"/>
       <c r="E3" s="5"/>
     </row>
-    <row r="4" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A4">
         <v>3</v>
       </c>
       <c r="C4" s="5"/>
       <c r="E4" s="5"/>
     </row>
-    <row r="5" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A5">
         <v>4</v>
       </c>
       <c r="C5" s="5"/>
       <c r="E5" s="5"/>
     </row>
-    <row r="6" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A6">
         <v>5</v>
       </c>
     </row>
-    <row r="7" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A7">
         <v>6</v>
       </c>
     </row>
-    <row r="8" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A8">
         <v>7</v>
       </c>
     </row>
-    <row r="9" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A9">
         <v>8</v>
       </c>
     </row>
-    <row r="10" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A10">
         <v>9</v>
       </c>
     </row>
-    <row r="11" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:6" x14ac:dyDescent="0.25">
       <c r="A11">
         <v>10</v>
       </c>
     </row>
-    <row r="15" spans="1:6" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:6" x14ac:dyDescent="0.25">
       <c r="C15" s="5"/>
       <c r="D15" s="5"/>
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
     </row>
-    <row r="17" spans="3:6" x14ac:dyDescent="0.3">
+    <row r="17" spans="3:6" x14ac:dyDescent="0.25">
       <c r="C17" s="5"/>
       <c r="D17" s="5"/>
       <c r="E17" s="5"/>
@@ -4999,12 +4999,12 @@
 <file path=xl/worksheets/sheet15.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{DBF5682F-29D1-41D2-B323-E6C39BD83827}">
   <dimension ref="A1:G1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="12.44140625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="12.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>128</v>
       </c>
@@ -5036,12 +5036,12 @@
 <file path=xl/worksheets/sheet16.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{02307C1F-427B-487D-B703-EBF512D7AC27}">
   <dimension ref="A1:C25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" style="5" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
@@ -5052,7 +5052,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
@@ -5064,7 +5064,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
@@ -5076,7 +5076,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
@@ -5088,7 +5088,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.124999826388</v>
@@ -5100,7 +5100,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666435187</v>
@@ -5112,7 +5112,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44671.208333043978</v>
@@ -5124,7 +5124,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44671.249999537038</v>
@@ -5136,7 +5136,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44671.291666087964</v>
@@ -5148,7 +5148,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44671.333332638889</v>
@@ -5160,7 +5160,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>44671.374999189815</v>
@@ -5172,85 +5172,85 @@
         <v>17</v>
       </c>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
@@ -5265,19 +5265,19 @@
 <file path=xl/worksheets/sheet17.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B3788A93-7501-4F5D-9E8F-38D329CC85EC}">
   <dimension ref="A1:L5"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="11" style="4" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="7.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.5546875" style="4" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="12.88671875" style="4" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.33203125" style="4" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.44140625" style="4" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="12.6640625" style="4" bestFit="1" customWidth="1"/>
-    <col min="8" max="16384" width="9.109375" style="4"/>
+    <col min="2" max="2" width="7.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.5703125" style="4" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="12.85546875" style="4" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.28515625" style="4" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.42578125" style="4" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="12.7109375" style="4" bestFit="1" customWidth="1"/>
+    <col min="8" max="16384" width="9.140625" style="4"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:12" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>25</v>
       </c>
@@ -5315,7 +5315,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A2" s="4" t="s">
         <v>10</v>
       </c>
@@ -5353,7 +5353,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A3" s="4" t="s">
         <v>59</v>
       </c>
@@ -5379,7 +5379,7 @@
         <v>1</v>
       </c>
       <c r="I3">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J3" s="4">
         <v>0</v>
@@ -5391,7 +5391,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A4" s="4" t="s">
         <v>78</v>
       </c>
@@ -5417,7 +5417,7 @@
         <v>1</v>
       </c>
       <c r="I4">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c r="J4" s="4">
         <v>0</v>
@@ -5429,7 +5429,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:12" x14ac:dyDescent="0.25">
       <c r="I5"/>
     </row>
   </sheetData>
@@ -5440,71 +5440,71 @@
 <file path=xl/worksheets/sheet18.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7B04689-3483-4889-8469-CD5E284D12AD}">
   <dimension ref="A1:A11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" style="5" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.124999826388</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666435187</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44671.208333043978</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44671.249999537038</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44671.291666087964</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44671.333332638889</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>44671.374999189815</v>
@@ -5519,13 +5519,13 @@
 <file path=xl/worksheets/sheet19.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A3E266E0-7523-413E-8B0C-F3E2413808A5}">
   <dimension ref="A1:E11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" style="5" customWidth="1"/>
-    <col min="2" max="3" width="6.5546875" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" style="5" customWidth="1"/>
+    <col min="2" max="3" width="6.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
@@ -5542,7 +5542,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
@@ -5560,7 +5560,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
@@ -5578,7 +5578,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
@@ -5596,7 +5596,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.124999826388</v>
@@ -5614,7 +5614,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666435187</v>
@@ -5632,7 +5632,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44671.208333043978</v>
@@ -5650,7 +5650,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44671.249999537038</v>
@@ -5668,7 +5668,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44671.291666087964</v>
@@ -5686,7 +5686,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44671.333332638889</v>
@@ -5704,7 +5704,7 @@
         <v>0.3</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>44671.374999189815</v>
@@ -5731,13 +5731,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5112C03D-AA3C-4BDB-99A8-E263BCF7A011}">
   <dimension ref="A1:B11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="27" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="5.88671875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="5.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>47</v>
       </c>
@@ -5745,7 +5745,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>110</v>
       </c>
@@ -5753,7 +5753,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>111</v>
       </c>
@@ -5761,7 +5761,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="4" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>112</v>
       </c>
@@ -5769,7 +5769,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="5" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>113</v>
       </c>
@@ -5777,7 +5777,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="6" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>114</v>
       </c>
@@ -5785,7 +5785,7 @@
         <v>1</v>
       </c>
     </row>
-    <row r="7" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>116</v>
       </c>
@@ -5793,7 +5793,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="8" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A8" t="s">
         <v>117</v>
       </c>
@@ -5801,7 +5801,7 @@
         <v>10000</v>
       </c>
     </row>
-    <row r="9" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A9" t="s">
         <v>126</v>
       </c>
@@ -5809,7 +5809,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A10" t="s">
         <v>127</v>
       </c>
@@ -5817,7 +5817,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A11" t="s">
         <v>115</v>
       </c>
@@ -5831,14 +5831,14 @@
 <file path=xl/worksheets/sheet20.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{EF6DDD9A-EF34-4108-8532-230729E9C708}">
   <dimension ref="A1:G11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" style="5" customWidth="1"/>
-    <col min="2" max="6" width="11.44140625" customWidth="1"/>
-    <col min="7" max="14" width="11.109375" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" style="5" customWidth="1"/>
+    <col min="2" max="6" width="11.42578125" customWidth="1"/>
+    <col min="7" max="14" width="11.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
@@ -5861,7 +5861,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
@@ -5885,7 +5885,7 @@
         <v>134.68</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
@@ -5909,7 +5909,7 @@
         <v>271.23</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
@@ -5933,7 +5933,7 @@
         <v>53.8</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.124999826388</v>
@@ -5957,7 +5957,7 @@
         <v>220.9</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666435187</v>
@@ -5981,7 +5981,7 @@
         <v>171.55</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44671.208333043978</v>
@@ -6005,7 +6005,7 @@
         <v>397.42</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44671.249999537038</v>
@@ -6029,7 +6029,7 @@
         <v>191.92</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44671.291666087964</v>
@@ -6053,7 +6053,7 @@
         <v>265.85000000000002</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44671.333332638889</v>
@@ -6077,7 +6077,7 @@
         <v>299.97000000000003</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>44671.374999189815</v>
@@ -6112,14 +6112,14 @@
 <file path=xl/worksheets/sheet21.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{817FDE8F-BC70-48D0-8376-FB52E6946AF1}">
   <dimension ref="A1:E25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="14.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="3" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="4" max="5" width="10.109375" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="14.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="3" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="4" max="5" width="10.140625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
@@ -6136,7 +6136,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
@@ -6158,7 +6158,7 @@
         <v>14.933999999999999</v>
       </c>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
@@ -6180,7 +6180,7 @@
         <v>6.7545000000000002</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
@@ -6202,7 +6202,7 @@
         <v>34.6845</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.124999826388</v>
@@ -6224,7 +6224,7 @@
         <v>26.847000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666435187</v>
@@ -6246,7 +6246,7 @@
         <v>44.735500000000002</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44671.208333043978</v>
@@ -6268,7 +6268,7 @@
         <v>31.805999999999994</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44671.249999537038</v>
@@ -6290,7 +6290,7 @@
         <v>64.998999999999995</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44671.291666087964</v>
@@ -6312,7 +6312,7 @@
         <v>61.474499999999992</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44671.333332638889</v>
@@ -6334,7 +6334,7 @@
         <v>9.1009999999999991</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>44671.374999189815</v>
@@ -6356,50 +6356,50 @@
         <v>22.486499999999999</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="5"/>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="5"/>
       <c r="B13" s="2"/>
       <c r="C13" s="2"/>
       <c r="D13" s="2"/>
       <c r="E13" s="2"/>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="5"/>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="5"/>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5"/>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="5"/>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="5"/>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="5"/>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="5"/>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="5"/>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="5"/>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="5"/>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="5"/>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="5"/>
     </row>
   </sheetData>
@@ -6411,13 +6411,13 @@
 <file path=xl/worksheets/sheet22.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{016E73B5-BC63-43DF-8AE1-9D3A59563F2A}">
   <dimension ref="A1:BA11"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" style="5" customWidth="1"/>
-    <col min="2" max="3" width="6.5546875" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" style="5" customWidth="1"/>
+    <col min="2" max="3" width="6.5703125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:53" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:53" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
@@ -6482,7 +6482,7 @@
       <c r="AZ1"/>
       <c r="BA1"/>
     </row>
-    <row r="2" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
@@ -6500,7 +6500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
@@ -6518,7 +6518,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
@@ -6536,7 +6536,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.124999826388</v>
@@ -6554,7 +6554,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666435187</v>
@@ -6572,7 +6572,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44671.208333043978</v>
@@ -6590,7 +6590,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44671.249999537038</v>
@@ -6608,7 +6608,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44671.291666087964</v>
@@ -6626,7 +6626,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44671.333332638889</v>
@@ -6644,7 +6644,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:53" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:53" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>44671.374999189815</v>
@@ -6670,12 +6670,12 @@
 <file path=xl/worksheets/sheet23.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{9314D326-256A-435C-AAE3-3517FA836EAE}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="10.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="10.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>47</v>
       </c>
@@ -6683,7 +6683,7 @@
         <v>48</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>49</v>
       </c>
@@ -6691,7 +6691,7 @@
         <v>0.1</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>50</v>
       </c>
@@ -6707,9 +6707,9 @@
 <file path=xl/worksheets/sheet24.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A87AD413-E614-48C1-80E1-F1E8236FCBC6}">
   <dimension ref="A1:B3"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:2" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>32</v>
       </c>
@@ -6717,7 +6717,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="2" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>34</v>
       </c>
@@ -6725,7 +6725,7 @@
         <v>0.5</v>
       </c>
     </row>
-    <row r="3" spans="1:2" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:2" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>35</v>
       </c>
@@ -6741,155 +6741,155 @@
 <file path=xl/worksheets/sheet25.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{31679CA5-0AA2-4F6F-8223-14BF74917F04}">
   <dimension ref="A1:A25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" style="5" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.124999826388</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666435187</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44671.208333043978</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44671.249999537038</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44671.291666087964</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44671.333332638889</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>44671.374999189815</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
@@ -6903,155 +6903,155 @@
 <file path=xl/worksheets/sheet26.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{FD670E02-665B-45B8-BC4E-9596D2C1BC55}">
   <dimension ref="A1:A25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" style="5" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.124999826388</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666435187</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44671.208333043978</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44671.249999537038</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44671.291666087964</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44671.333332638889</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>44671.374999189815</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
@@ -7066,155 +7066,155 @@
 <file path=xl/worksheets/sheet27.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{A7FEDBA5-B0F3-4E9D-9367-08D5F5FA8AEA}">
   <dimension ref="A1:A25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" style="5" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.124999826388</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666435187</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44671.208333043978</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44671.249999537038</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44671.291666087964</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44671.333332638889</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>44671.374999189815</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
@@ -7228,14 +7228,14 @@
 <file path=xl/worksheets/sheet28.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5704FC51-737E-45F9-9A9E-85A96AFE5439}">
   <dimension ref="A1:M9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="17.6640625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="22.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="25.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="17.7109375" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="22.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="25.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A1" t="s">
         <v>32</v>
       </c>
@@ -7249,7 +7249,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="2" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>82</v>
       </c>
@@ -7263,7 +7263,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:13" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:13" x14ac:dyDescent="0.25">
       <c r="K9" s="2"/>
       <c r="L9" s="2"/>
       <c r="M9" s="2"/>
@@ -7277,15 +7277,15 @@
 <file path=xl/worksheets/sheet29.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{BE12AB76-2BDA-4ACA-A128-8CFB9FB6C8F8}">
   <dimension ref="A1:G25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" style="5" customWidth="1"/>
-    <col min="2" max="4" width="14.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="7" width="14.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="10" width="5.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" style="5" customWidth="1"/>
+    <col min="2" max="4" width="14.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="7" width="14.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="10" width="5.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
@@ -7308,7 +7308,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="2" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
@@ -7332,7 +7332,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
@@ -7356,7 +7356,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
@@ -7380,7 +7380,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="5" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.124999826388</v>
@@ -7404,7 +7404,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="6" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666435187</v>
@@ -7428,7 +7428,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="7" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44671.208333043978</v>
@@ -7452,7 +7452,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="8" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44671.249999537038</v>
@@ -7476,7 +7476,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44671.291666087964</v>
@@ -7500,7 +7500,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="10" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44671.333332638889</v>
@@ -7524,7 +7524,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="11" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>44671.374999189815</v>
@@ -7548,85 +7548,85 @@
         <v>0</v>
       </c>
     </row>
-    <row r="12" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:7" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
@@ -7640,20 +7640,20 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{04A1B16B-CDA9-46BD-BA51-731AA9327652}">
   <dimension ref="A1:P4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.88671875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="6.109375" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.6640625" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="9.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="7.44140625" bestFit="1" customWidth="1"/>
-    <col min="9" max="9" width="8.6640625" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5703125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.85546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.7109375" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="9.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="7.42578125" bestFit="1" customWidth="1"/>
+    <col min="9" max="9" width="8.7109375" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:16" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -7703,7 +7703,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>7</v>
       </c>
@@ -7753,7 +7753,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -7803,7 +7803,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:16" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>70</v>
       </c>
@@ -7861,22 +7861,22 @@
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{CB20090B-02A9-43B7-8D03-9C18D42920EB}">
   <dimension ref="A1:Q9"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.88671875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.85546875" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="5" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="6.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.6640625" customWidth="1"/>
+    <col min="3" max="3" width="8.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="6.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.7109375" customWidth="1"/>
     <col min="7" max="7" width="5" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="9.33203125" bestFit="1" customWidth="1"/>
-    <col min="9" max="10" width="9.5546875" bestFit="1" customWidth="1"/>
-    <col min="11" max="11" width="11.109375" bestFit="1" customWidth="1"/>
-    <col min="12" max="12" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="13" max="14" width="11.44140625" customWidth="1"/>
+    <col min="8" max="8" width="9.28515625" bestFit="1" customWidth="1"/>
+    <col min="9" max="10" width="9.5703125" bestFit="1" customWidth="1"/>
+    <col min="11" max="11" width="11.140625" bestFit="1" customWidth="1"/>
+    <col min="12" max="12" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="13" max="14" width="11.42578125" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:17" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -7929,7 +7929,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="2" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>71</v>
       </c>
@@ -7982,7 +7982,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="3" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>73</v>
       </c>
@@ -8035,7 +8035,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="4" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:17" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>72</v>
       </c>
@@ -8088,7 +8088,7 @@
         <v>0</v>
       </c>
     </row>
-    <row r="9" spans="1:17" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:17" x14ac:dyDescent="0.25">
       <c r="Q9" s="2"/>
     </row>
   </sheetData>
@@ -8099,9 +8099,9 @@
 <file path=xl/worksheets/sheet5.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{5539A729-4FB7-440D-A765-676495DE3453}">
   <dimension ref="A1:C4"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>125</v>
       </c>
@@ -8112,7 +8112,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>0</v>
       </c>
@@ -8123,7 +8123,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>11</v>
       </c>
@@ -8134,7 +8134,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>11</v>
       </c>
@@ -8153,9 +8153,9 @@
 <file path=xl/worksheets/sheet6.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{AAB1106B-D567-41FC-8E91-2B4CC5EC9B59}">
   <dimension ref="A1:K1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <sheetData>
-    <row r="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:11" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -8207,19 +8207,19 @@
 <file path=xl/worksheets/sheet7.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{8A86A8A7-FD76-4891-A53C-CBB095359118}">
   <dimension ref="A1:J7"/>
-  <sheetFormatPr defaultColWidth="9.109375" defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultColWidth="9.140625" defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="16.88671875" bestFit="1" customWidth="1"/>
-    <col min="2" max="2" width="11.44140625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="5.5546875" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="16.44140625" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="8.109375" bestFit="1" customWidth="1"/>
-    <col min="6" max="6" width="10.109375" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="8.88671875" bestFit="1" customWidth="1"/>
-    <col min="8" max="8" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="1" max="1" width="16.85546875" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.42578125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="5.5703125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="16.42578125" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="8.140625" bestFit="1" customWidth="1"/>
+    <col min="6" max="6" width="10.140625" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="8.85546875" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="11.5703125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:10" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>11</v>
       </c>
@@ -8251,7 +8251,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="2" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A2" t="s">
         <v>71</v>
       </c>
@@ -8283,7 +8283,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="3" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A3" t="s">
         <v>71</v>
       </c>
@@ -8315,7 +8315,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="4" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A4" t="s">
         <v>71</v>
       </c>
@@ -8347,7 +8347,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="5" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A5" t="s">
         <v>73</v>
       </c>
@@ -8379,7 +8379,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="6" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A6" t="s">
         <v>72</v>
       </c>
@@ -8411,7 +8411,7 @@
         <v>0.7</v>
       </c>
     </row>
-    <row r="7" spans="1:10" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:10" x14ac:dyDescent="0.25">
       <c r="A7" t="s">
         <v>72</v>
       </c>
@@ -8452,155 +8452,155 @@
 <file path=xl/worksheets/sheet8.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{B7AEF404-3743-47D7-AC45-7AE3A9FB796E}">
   <dimension ref="A1:A25"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="1" width="19.33203125" style="5" customWidth="1"/>
+    <col min="1" max="1" width="19.28515625" style="5" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>24</v>
       </c>
     </row>
-    <row r="2" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="2" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A2" s="5">
         <f>IF(timeseries!A2&lt;&gt;"",timeseries!A2,"")</f>
         <v>44671</v>
       </c>
     </row>
-    <row r="3" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="3" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A3" s="5">
         <f>IF(timeseries!A3&lt;&gt;"",timeseries!A3,"")</f>
         <v>44671.041666666664</v>
       </c>
     </row>
-    <row r="4" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="4" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <f>IF(timeseries!A4&lt;&gt;"",timeseries!A4,"")</f>
         <v>44671.08333321759</v>
       </c>
     </row>
-    <row r="5" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="5" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <f>IF(timeseries!A5&lt;&gt;"",timeseries!A5,"")</f>
         <v>44671.124999826388</v>
       </c>
     </row>
-    <row r="6" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="6" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <f>IF(timeseries!A6&lt;&gt;"",timeseries!A6,"")</f>
         <v>44671.166666435187</v>
       </c>
     </row>
-    <row r="7" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="7" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <f>IF(timeseries!A7&lt;&gt;"",timeseries!A7,"")</f>
         <v>44671.208333043978</v>
       </c>
     </row>
-    <row r="8" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="8" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <f>IF(timeseries!A8&lt;&gt;"",timeseries!A8,"")</f>
         <v>44671.249999537038</v>
       </c>
     </row>
-    <row r="9" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="9" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <f>IF(timeseries!A9&lt;&gt;"",timeseries!A9,"")</f>
         <v>44671.291666087964</v>
       </c>
     </row>
-    <row r="10" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="10" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <f>IF(timeseries!A10&lt;&gt;"",timeseries!A10,"")</f>
         <v>44671.333332638889</v>
       </c>
     </row>
-    <row r="11" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="11" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <f>IF(timeseries!A11&lt;&gt;"",timeseries!A11,"")</f>
         <v>44671.374999189815</v>
       </c>
     </row>
-    <row r="12" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="12" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A12" s="5" t="str">
         <f>IF(timeseries!A12&lt;&gt;"",timeseries!A12,"")</f>
         <v/>
       </c>
     </row>
-    <row r="13" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="13" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A13" s="5" t="str">
         <f>IF(timeseries!A13&lt;&gt;"",timeseries!A13,"")</f>
         <v/>
       </c>
     </row>
-    <row r="14" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="14" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A14" s="5" t="str">
         <f>IF(timeseries!A14&lt;&gt;"",timeseries!A14,"")</f>
         <v/>
       </c>
     </row>
-    <row r="15" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="15" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A15" s="5" t="str">
         <f>IF(timeseries!A15&lt;&gt;"",timeseries!A15,"")</f>
         <v/>
       </c>
     </row>
-    <row r="16" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="16" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A16" s="5" t="str">
         <f>IF(timeseries!A16&lt;&gt;"",timeseries!A16,"")</f>
         <v/>
       </c>
     </row>
-    <row r="17" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="17" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A17" s="5" t="str">
         <f>IF(timeseries!A17&lt;&gt;"",timeseries!A17,"")</f>
         <v/>
       </c>
     </row>
-    <row r="18" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="18" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A18" s="5" t="str">
         <f>IF(timeseries!A18&lt;&gt;"",timeseries!A18,"")</f>
         <v/>
       </c>
     </row>
-    <row r="19" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="19" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A19" s="5" t="str">
         <f>IF(timeseries!A19&lt;&gt;"",timeseries!A19,"")</f>
         <v/>
       </c>
     </row>
-    <row r="20" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="20" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A20" s="5" t="str">
         <f>IF(timeseries!A20&lt;&gt;"",timeseries!A20,"")</f>
         <v/>
       </c>
     </row>
-    <row r="21" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="21" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A21" s="5" t="str">
         <f>IF(timeseries!A21&lt;&gt;"",timeseries!A21,"")</f>
         <v/>
       </c>
     </row>
-    <row r="22" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="22" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A22" s="5" t="str">
         <f>IF(timeseries!A22&lt;&gt;"",timeseries!A22,"")</f>
         <v/>
       </c>
     </row>
-    <row r="23" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="23" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A23" s="5" t="str">
         <f>IF(timeseries!A23&lt;&gt;"",timeseries!A23,"")</f>
         <v/>
       </c>
     </row>
-    <row r="24" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="24" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A24" s="5" t="str">
         <f>IF(timeseries!A24&lt;&gt;"",timeseries!A24,"")</f>
         <v/>
       </c>
     </row>
-    <row r="25" spans="1:1" x14ac:dyDescent="0.3">
+    <row r="25" spans="1:1" x14ac:dyDescent="0.25">
       <c r="A25" s="5" t="str">
         <f>IF(timeseries!A25&lt;&gt;"",timeseries!A25,"")</f>
         <v/>
@@ -8614,14 +8614,14 @@
 <file path=xl/worksheets/sheet9.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{596E3FE2-967D-4C0B-BDAC-EF3704EC4DDF}">
   <dimension ref="A1:E1"/>
-  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
-    <col min="1" max="2" width="6.33203125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="7.33203125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="9.33203125" bestFit="1" customWidth="1"/>
+    <col min="1" max="2" width="6.28515625" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="7.28515625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="9.28515625" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.3">
+    <row r="1" spans="1:5" s="2" customFormat="1" x14ac:dyDescent="0.25">
       <c r="A1" s="2" t="s">
         <v>99</v>
       </c>
